--- a/source_data/GLM_Figures.xlsx
+++ b/source_data/GLM_Figures.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="88">
   <si>
     <t>Sheet</t>
   </si>
@@ -724,7 +724,7 @@
         <v>21</v>
       </c>
       <c r="D10">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -786,16 +786,16 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>1.475899199196198</v>
+        <v>1.475543993495024</v>
       </c>
       <c r="F2">
-        <v>1.191963434697877</v>
+        <v>1.192036182131781</v>
       </c>
       <c r="G2">
-        <v>1.827470862594119</v>
+        <v>1.826479858057318</v>
       </c>
       <c r="H2">
-        <v>0.0003559355607520878</v>
+        <v>0.0003520973826396771</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>37</v>
       </c>
       <c r="K2">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -821,16 +821,16 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>1.003667944596689</v>
+        <v>1.003662413238331</v>
       </c>
       <c r="F3">
-        <v>1.001655020699057</v>
+        <v>1.001647685592979</v>
       </c>
       <c r="G3">
-        <v>1.005684913662101</v>
+        <v>1.005681193334005</v>
       </c>
       <c r="H3">
-        <v>0.0003510400294561127</v>
+        <v>0.0003627543332437352</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -839,7 +839,7 @@
         <v>37</v>
       </c>
       <c r="K3">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -856,25 +856,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>1.199878940617643</v>
+        <v>1.207480461181033</v>
       </c>
       <c r="F4">
-        <v>1.047399376522188</v>
+        <v>0.9946875499692609</v>
       </c>
       <c r="G4">
-        <v>1.37455635778414</v>
+        <v>1.465796032310867</v>
       </c>
       <c r="H4">
-        <v>0.008593772353924105</v>
+        <v>0.05663573228797841</v>
       </c>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>37</v>
       </c>
       <c r="K4">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -891,16 +891,16 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>1.002570217055736</v>
+        <v>1.002702451117742</v>
       </c>
       <c r="F5">
-        <v>1.001097978180742</v>
+        <v>1.000963139776224</v>
       </c>
       <c r="G5">
-        <v>1.004044621040791</v>
+        <v>1.004444784752311</v>
       </c>
       <c r="H5">
-        <v>0.0006180682200781371</v>
+        <v>0.00231325946859411</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>37</v>
       </c>
       <c r="K5">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -926,16 +926,16 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>1.331547433091261</v>
+        <v>1.498455786427848</v>
       </c>
       <c r="F6">
-        <v>1.072326067404032</v>
+        <v>1.177161167537141</v>
       </c>
       <c r="G6">
-        <v>1.65343230987957</v>
+        <v>1.907444626785359</v>
       </c>
       <c r="H6">
-        <v>0.009539218419721157</v>
+        <v>0.001021154705932156</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -944,7 +944,7 @@
         <v>37</v>
       </c>
       <c r="K6">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -961,16 +961,16 @@
         <v>38</v>
       </c>
       <c r="E7">
-        <v>1.001134249205653</v>
+        <v>0.9995347775030099</v>
       </c>
       <c r="F7">
-        <v>0.9986479022262917</v>
+        <v>0.9958728205279409</v>
       </c>
       <c r="G7">
-        <v>1.003626786476195</v>
+        <v>1.003210199981516</v>
       </c>
       <c r="H7">
-        <v>0.3715822394168474</v>
+        <v>0.8037602527530885</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>37</v>
       </c>
       <c r="K7">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -996,16 +996,16 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>1.475899199196198</v>
+        <v>1.475543993495024</v>
       </c>
       <c r="F8">
-        <v>1.40626145340346</v>
+        <v>1.405967792966609</v>
       </c>
       <c r="G8">
-        <v>1.548985390245937</v>
+        <v>1.548563265553375</v>
       </c>
       <c r="H8">
-        <v>3.096792417788414E-54</v>
+        <v>3.037208440380459E-54</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -1014,7 +1014,7 @@
         <v>42</v>
       </c>
       <c r="K8">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1031,16 +1031,16 @@
         <v>38</v>
       </c>
       <c r="E9">
-        <v>1.003667944596689</v>
+        <v>1.003662413238331</v>
       </c>
       <c r="F9">
-        <v>1.002797736163836</v>
+        <v>1.002792647200661</v>
       </c>
       <c r="G9">
-        <v>1.004538908179548</v>
+        <v>1.004532933662228</v>
       </c>
       <c r="H9">
-        <v>1.820392343641372E-16</v>
+        <v>1.947406272210221E-16</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -1049,7 +1049,7 @@
         <v>42</v>
       </c>
       <c r="K9">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1066,16 +1066,16 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>1.199878940617643</v>
+        <v>1.207480461181033</v>
       </c>
       <c r="F10">
-        <v>1.142599298391013</v>
+        <v>1.138106714361758</v>
       </c>
       <c r="G10">
-        <v>1.260030068428267</v>
+        <v>1.28108291229228</v>
       </c>
       <c r="H10">
-        <v>3.47660225033063E-13</v>
+        <v>4.699533644132732E-10</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -1084,7 +1084,7 @@
         <v>42</v>
       </c>
       <c r="K10">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1101,16 +1101,16 @@
         <v>38</v>
       </c>
       <c r="E11">
-        <v>1.002570217055736</v>
+        <v>1.002702451117742</v>
       </c>
       <c r="F11">
-        <v>1.001774096150571</v>
+        <v>1.001784824541493</v>
       </c>
       <c r="G11">
-        <v>1.003366970646949</v>
+        <v>1.003620918232311</v>
       </c>
       <c r="H11">
-        <v>2.682581141170983E-10</v>
+        <v>8.183277726942792E-09</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
         <v>42</v>
       </c>
       <c r="K11">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1136,16 +1136,16 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>1.331547433091261</v>
+        <v>1.498455786427848</v>
       </c>
       <c r="F12">
-        <v>1.240688465519196</v>
+        <v>1.359722500757371</v>
       </c>
       <c r="G12">
-        <v>1.429060248279138</v>
+        <v>1.651344110749377</v>
       </c>
       <c r="H12">
-        <v>2.665869342611628E-15</v>
+        <v>4.620107919482388E-16</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1154,7 +1154,7 @@
         <v>42</v>
       </c>
       <c r="K12">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1171,25 +1171,25 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>1.001134249205653</v>
+        <v>0.9995347775030099</v>
       </c>
       <c r="F13">
-        <v>1.000044263646365</v>
+        <v>0.9981177664252772</v>
       </c>
       <c r="G13">
-        <v>1.002225422780874</v>
+        <v>1.000953800287639</v>
       </c>
       <c r="H13">
-        <v>0.04139487020345321</v>
+        <v>0.5201983544625741</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="s">
         <v>42</v>
       </c>
       <c r="K13">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1206,16 +1206,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>1.104087339986717</v>
+        <v>1.10560075343979</v>
       </c>
       <c r="F14">
-        <v>1.024526666525178</v>
+        <v>1.026483544259008</v>
       </c>
       <c r="G14">
-        <v>1.18982637948642</v>
+        <v>1.190815997823928</v>
       </c>
       <c r="H14">
-        <v>0.009459811836170973</v>
+        <v>0.008050387105388713</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>37</v>
       </c>
       <c r="K14">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1241,16 +1241,16 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>1.002591249638505</v>
+        <v>1.002598358415663</v>
       </c>
       <c r="F15">
-        <v>1.001241991282686</v>
+        <v>1.001254736647222</v>
       </c>
       <c r="G15">
-        <v>1.003942326234198</v>
+        <v>1.003943783241199</v>
       </c>
       <c r="H15">
-        <v>0.000165588319610387</v>
+        <v>0.000149050506065006</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -1259,7 +1259,7 @@
         <v>37</v>
       </c>
       <c r="K15">
-        <v>3389</v>
+        <v>3397</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1276,16 +1276,16 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>1.053731213029229</v>
+        <v>1.028988072881243</v>
       </c>
       <c r="F16">
-        <v>0.9894129615235745</v>
+        <v>0.9482737070027258</v>
       </c>
       <c r="G16">
-        <v>1.122230567509697</v>
+        <v>1.116572616442703</v>
       </c>
       <c r="H16">
-        <v>0.1033682687479647</v>
+        <v>0.4929468506980929</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>37</v>
       </c>
       <c r="K16">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1311,25 +1311,25 @@
         <v>38</v>
       </c>
       <c r="E17">
-        <v>1.001687044263111</v>
+        <v>1.001448290598608</v>
       </c>
       <c r="F17">
-        <v>1.000537057197977</v>
+        <v>0.9997467704250891</v>
       </c>
       <c r="G17">
-        <v>1.002838353088634</v>
+        <v>1.003152706676356</v>
       </c>
       <c r="H17">
-        <v>0.004026711971050116</v>
+        <v>0.09530377756332478</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="s">
         <v>37</v>
       </c>
       <c r="K17">
-        <v>3375</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1346,16 +1346,16 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>1.091252845551442</v>
+        <v>1.105729872724961</v>
       </c>
       <c r="F18">
-        <v>1.006303609811841</v>
+        <v>1.001462802515169</v>
       </c>
       <c r="G18">
-        <v>1.183373249696264</v>
+        <v>1.220852685058004</v>
       </c>
       <c r="H18">
-        <v>0.03469208500519163</v>
+        <v>0.04671334589159497</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         <v>37</v>
       </c>
       <c r="K18">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1381,25 +1381,25 @@
         <v>38</v>
       </c>
       <c r="E19">
-        <v>1.001488580902232</v>
+        <v>1.001020737410117</v>
       </c>
       <c r="F19">
-        <v>1.000387310361022</v>
+        <v>0.999702635934694</v>
       </c>
       <c r="G19">
-        <v>1.002591063770699</v>
+        <v>1.00234057679383</v>
       </c>
       <c r="H19">
-        <v>0.008054309025600628</v>
+        <v>0.1291228561338711</v>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="s">
         <v>37</v>
       </c>
       <c r="K19">
-        <v>3348</v>
+        <v>3385</v>
       </c>
     </row>
   </sheetData>
@@ -1449,16 +1449,16 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>1.061332787233738</v>
+        <v>1.056714435432698</v>
       </c>
       <c r="E2">
-        <v>0.9132829442422919</v>
+        <v>0.9089721635370156</v>
       </c>
       <c r="F2">
-        <v>1.233382592282919</v>
+        <v>1.228470400795033</v>
       </c>
       <c r="G2">
-        <v>0.4374134134941706</v>
+        <v>0.4728153088516416</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1475,16 +1475,16 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>1.003215201590385</v>
+        <v>1.003229356309664</v>
       </c>
       <c r="E3">
-        <v>1.001055086718301</v>
+        <v>1.001066121801487</v>
       </c>
       <c r="F3">
-        <v>1.005379977640782</v>
+        <v>1.005397265417686</v>
       </c>
       <c r="G3">
-        <v>0.003513512821085847</v>
+        <v>0.003417373666556776</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -1501,16 +1501,16 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>1.297897627290496</v>
+        <v>1.31269863640097</v>
       </c>
       <c r="E4">
-        <v>0.7880330850449735</v>
+        <v>0.8007206444848736</v>
       </c>
       <c r="F4">
-        <v>2.137649145568758</v>
+        <v>2.152033573603606</v>
       </c>
       <c r="G4">
-        <v>0.3057252350829428</v>
+        <v>0.2806808349943211</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -1527,16 +1527,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>1.006357317876335</v>
+        <v>1.00637747622965</v>
       </c>
       <c r="E5">
-        <v>1.002213583174068</v>
+        <v>1.002236711144921</v>
       </c>
       <c r="F5">
-        <v>1.010518185191422</v>
+        <v>1.010535348984948</v>
       </c>
       <c r="G5">
-        <v>0.002609896420016327</v>
+        <v>0.002510723575060639</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -1553,16 +1553,16 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>3.862423238310198</v>
+        <v>3.860225971868828</v>
       </c>
       <c r="E6">
-        <v>1.894136206516865</v>
+        <v>1.892487413930742</v>
       </c>
       <c r="F6">
-        <v>7.876050951621889</v>
+        <v>7.873946449630639</v>
       </c>
       <c r="G6">
-        <v>0.0002015933206724933</v>
+        <v>0.0002041111880753546</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -1579,16 +1579,16 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>1.004398142171862</v>
+        <v>1.004396335303877</v>
       </c>
       <c r="E7">
-        <v>1.001291958522772</v>
+        <v>1.00128872475704</v>
       </c>
       <c r="F7">
-        <v>1.007513961748594</v>
+        <v>1.007513590664514</v>
       </c>
       <c r="G7">
-        <v>0.005486907740558856</v>
+        <v>0.005527895555117682</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -1605,16 +1605,16 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>1.154081417235259</v>
+        <v>1.162165388035748</v>
       </c>
       <c r="E8">
-        <v>0.9051796726105398</v>
+        <v>0.9133948850984145</v>
       </c>
       <c r="F8">
-        <v>1.471424909229932</v>
+        <v>1.478690554526979</v>
       </c>
       <c r="G8">
-        <v>0.2475986516211962</v>
+        <v>0.2213818500542375</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>0.999660395939032</v>
+        <v>0.9996873006338888</v>
       </c>
       <c r="E9">
-        <v>0.9969011186268022</v>
+        <v>0.9969272529042714</v>
       </c>
       <c r="F9">
-        <v>1.002427310529567</v>
+        <v>1.002454989706892</v>
       </c>
       <c r="G9">
-        <v>0.8096691649572114</v>
+        <v>0.824537622692197</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>36</v>
       </c>
       <c r="D10">
-        <v>1.792531771444922</v>
+        <v>1.807151754191344</v>
       </c>
       <c r="E10">
-        <v>1.233824698489254</v>
+        <v>1.24926204359737</v>
       </c>
       <c r="F10">
-        <v>2.604235557590808</v>
+        <v>2.614181291598897</v>
       </c>
       <c r="G10">
-        <v>0.002194631295855725</v>
+        <v>0.001681252370134909</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1683,16 +1683,16 @@
         <v>38</v>
       </c>
       <c r="D11">
-        <v>1.006055032341569</v>
+        <v>1.00609742473109</v>
       </c>
       <c r="E11">
-        <v>1.002052018058762</v>
+        <v>1.002115289355005</v>
       </c>
       <c r="F11">
-        <v>1.01007403793327</v>
+        <v>1.010095384037137</v>
       </c>
       <c r="G11">
-        <v>0.003000224518672711</v>
+        <v>0.002662309569892121</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1709,16 +1709,16 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>1.059995694321848</v>
+        <v>1.059364192691061</v>
       </c>
       <c r="E12">
-        <v>0.7635672386379612</v>
+        <v>0.7630413384566318</v>
       </c>
       <c r="F12">
-        <v>1.471502200624926</v>
+        <v>1.470762377076333</v>
       </c>
       <c r="G12">
-        <v>0.727733930588601</v>
+        <v>0.730483107915646</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -1735,16 +1735,16 @@
         <v>38</v>
       </c>
       <c r="D13">
-        <v>1.002420295696785</v>
+        <v>1.002414011679211</v>
       </c>
       <c r="E13">
-        <v>0.9978616454773995</v>
+        <v>0.9978555476313042</v>
       </c>
       <c r="F13">
-        <v>1.00699977174099</v>
+        <v>1.006993299978208</v>
       </c>
       <c r="G13">
-        <v>0.2985820592717648</v>
+        <v>0.2998201236671125</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -1761,16 +1761,16 @@
         <v>36</v>
       </c>
       <c r="D14">
-        <v>1.826955941952724</v>
+        <v>1.82603404300949</v>
       </c>
       <c r="E14">
-        <v>1.13974596034966</v>
+        <v>1.138415143377685</v>
       </c>
       <c r="F14">
-        <v>2.928519275306209</v>
+        <v>2.928984514679236</v>
       </c>
       <c r="G14">
-        <v>0.01230389404911613</v>
+        <v>0.01250029075135707</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1787,16 +1787,16 @@
         <v>38</v>
       </c>
       <c r="D15">
-        <v>1.00579085769352</v>
+        <v>1.0057884005098</v>
       </c>
       <c r="E15">
-        <v>1.001115724535675</v>
+        <v>1.00111148721907</v>
       </c>
       <c r="F15">
-        <v>1.01048782336234</v>
+        <v>1.010487163033315</v>
       </c>
       <c r="G15">
-        <v>0.01513786645159253</v>
+        <v>0.01521989864522346</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1813,16 +1813,16 @@
         <v>36</v>
       </c>
       <c r="D16">
-        <v>1.743498731076022</v>
+        <v>1.62714357040853</v>
       </c>
       <c r="E16">
-        <v>1.265848566853216</v>
+        <v>1.151900877030109</v>
       </c>
       <c r="F16">
-        <v>2.401383471026345</v>
+        <v>2.298458358281652</v>
       </c>
       <c r="G16">
-        <v>0.0006660644161850444</v>
+        <v>0.005738122783153863</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1839,16 +1839,16 @@
         <v>38</v>
       </c>
       <c r="D17">
-        <v>1.002917065081515</v>
+        <v>1.002382176266166</v>
       </c>
       <c r="E17">
-        <v>0.9988683212945425</v>
+        <v>0.9983275616728809</v>
       </c>
       <c r="F17">
-        <v>1.006982219766605</v>
+        <v>1.00645325829973</v>
       </c>
       <c r="G17">
-        <v>0.1581477115619413</v>
+        <v>0.249913450323273</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
@@ -1865,16 +1865,16 @@
         <v>36</v>
       </c>
       <c r="D18">
-        <v>1.186041994534543</v>
+        <v>1.191165373489334</v>
       </c>
       <c r="E18">
-        <v>0.9815221604475921</v>
+        <v>0.9852500461178791</v>
       </c>
       <c r="F18">
-        <v>1.433177639267969</v>
+        <v>1.440116600441373</v>
       </c>
       <c r="G18">
-        <v>0.07725647594607588</v>
+        <v>0.07083902065975517</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
@@ -1891,16 +1891,16 @@
         <v>38</v>
       </c>
       <c r="D19">
-        <v>1.00240564590738</v>
+        <v>1.002467122872027</v>
       </c>
       <c r="E19">
-        <v>0.9987957890414886</v>
+        <v>0.9988580727625004</v>
       </c>
       <c r="F19">
-        <v>1.006028549550935</v>
+        <v>1.006089213115131</v>
       </c>
       <c r="G19">
-        <v>0.1917723445723913</v>
+        <v>0.18055320962723</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
@@ -1917,16 +1917,16 @@
         <v>36</v>
       </c>
       <c r="D20">
-        <v>1.782968501945143</v>
+        <v>1.825259116570878</v>
       </c>
       <c r="E20">
-        <v>1.185513538245327</v>
+        <v>1.211537909014057</v>
       </c>
       <c r="F20">
-        <v>2.681518663746089</v>
+        <v>2.749869251170454</v>
       </c>
       <c r="G20">
-        <v>0.005482036048487182</v>
+        <v>0.004006431250359586</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1943,16 +1943,16 @@
         <v>38</v>
       </c>
       <c r="D21">
-        <v>1.001753818860061</v>
+        <v>1.001843951926406</v>
       </c>
       <c r="E21">
-        <v>0.9978885407352994</v>
+        <v>0.9979754982785896</v>
       </c>
       <c r="F21">
-        <v>1.005634068972547</v>
+        <v>1.005727400865842</v>
       </c>
       <c r="G21">
-        <v>0.3743423878323908</v>
+        <v>0.3506660147475591</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1969,16 +1969,16 @@
         <v>36</v>
       </c>
       <c r="D22">
-        <v>1.137249252522957</v>
+        <v>1.134663241937479</v>
       </c>
       <c r="E22">
-        <v>0.9397077876931609</v>
+        <v>0.9363997329232527</v>
       </c>
       <c r="F22">
-        <v>1.376317062923322</v>
+        <v>1.374904997660428</v>
       </c>
       <c r="G22">
-        <v>0.1864479391076719</v>
+        <v>0.197284056492373</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -1995,16 +1995,16 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>0.9987996390227013</v>
+        <v>0.9988195049485886</v>
       </c>
       <c r="E23">
-        <v>0.9960861539089668</v>
+        <v>0.9961027235714907</v>
       </c>
       <c r="F23">
-        <v>1.001520516068784</v>
+        <v>1.001543696104695</v>
       </c>
       <c r="G23">
-        <v>0.3868584382290646</v>
+        <v>0.395335078228805</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
@@ -2021,16 +2021,16 @@
         <v>36</v>
       </c>
       <c r="D24">
-        <v>1.038098206095153</v>
+        <v>1.035999224283278</v>
       </c>
       <c r="E24">
-        <v>0.8327920873813571</v>
+        <v>0.8309490678716176</v>
       </c>
       <c r="F24">
-        <v>1.294017920951368</v>
+        <v>1.29164883169636</v>
       </c>
       <c r="G24">
-        <v>0.7394652482047314</v>
+        <v>0.7533035319994965</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
@@ -2047,16 +2047,16 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>1.002301286685225</v>
+        <v>1.002350689788738</v>
       </c>
       <c r="E25">
-        <v>0.9968242299935635</v>
+        <v>0.9968696169522581</v>
       </c>
       <c r="F25">
-        <v>1.007808437097627</v>
+        <v>1.007861899123439</v>
       </c>
       <c r="G25">
-        <v>0.4109589335767165</v>
+        <v>0.4013224074787327</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2073,16 +2073,16 @@
         <v>36</v>
       </c>
       <c r="D26">
-        <v>2.243053342052165</v>
+        <v>2.248698418309647</v>
       </c>
       <c r="E26">
-        <v>1.681798606253442</v>
+        <v>1.685081826032201</v>
       </c>
       <c r="F26">
-        <v>2.991611645165785</v>
+        <v>3.000830285147042</v>
       </c>
       <c r="G26">
-        <v>3.837358373874807E-08</v>
+        <v>3.701772088163586E-08</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -2099,16 +2099,16 @@
         <v>38</v>
       </c>
       <c r="D27">
-        <v>1.004607758283129</v>
+        <v>1.004708449394507</v>
       </c>
       <c r="E27">
-        <v>0.9997480389351668</v>
+        <v>0.9998759409025486</v>
       </c>
       <c r="F27">
-        <v>1.009491100455265</v>
+        <v>1.009564313922318</v>
       </c>
       <c r="G27">
-        <v>0.06315309543067182</v>
+        <v>0.0561937741862457</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D28">
-        <v>2.41360458941741</v>
+        <v>2.438401392462969</v>
       </c>
       <c r="E28">
-        <v>1.803949445190723</v>
+        <v>1.823090377434055</v>
       </c>
       <c r="F28">
-        <v>3.229296214252214</v>
+        <v>3.261385954509772</v>
       </c>
       <c r="G28">
-        <v>2.998540997817902E-09</v>
+        <v>1.885620054667856E-09</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -2151,16 +2151,16 @@
         <v>38</v>
       </c>
       <c r="D29">
-        <v>1.005403301082382</v>
+        <v>1.005440098072981</v>
       </c>
       <c r="E29">
-        <v>1.002905530282115</v>
+        <v>1.002948753095876</v>
       </c>
       <c r="F29">
-        <v>1.007907292666942</v>
+        <v>1.007937631601371</v>
       </c>
       <c r="G29">
-        <v>2.175799710974723E-05</v>
+        <v>1.818565195596919E-05</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -2177,16 +2177,16 @@
         <v>36</v>
       </c>
       <c r="D30">
-        <v>0.7327446472218286</v>
+        <v>0.7371477453341434</v>
       </c>
       <c r="E30">
-        <v>0.5493692643380499</v>
+        <v>0.5531413673353172</v>
       </c>
       <c r="F30">
-        <v>0.9773293718555321</v>
+        <v>0.9823651430535789</v>
       </c>
       <c r="G30">
-        <v>0.03434406087895316</v>
+        <v>0.0373977154245982</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -2203,16 +2203,16 @@
         <v>38</v>
       </c>
       <c r="D31">
-        <v>1.001933290893109</v>
+        <v>1.001966761756116</v>
       </c>
       <c r="E31">
-        <v>0.9981228496472757</v>
+        <v>0.9981597575594522</v>
       </c>
       <c r="F31">
-        <v>1.005758278907904</v>
+        <v>1.005788285954055</v>
       </c>
       <c r="G31">
-        <v>0.3204726467905382</v>
+        <v>0.311720554845729</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -2229,16 +2229,16 @@
         <v>36</v>
       </c>
       <c r="D32">
-        <v>1.454299226713854</v>
+        <v>1.449855870333512</v>
       </c>
       <c r="E32">
-        <v>1.171539085897946</v>
+        <v>1.166411652898281</v>
       </c>
       <c r="F32">
-        <v>1.805305743768205</v>
+        <v>1.802178535783081</v>
       </c>
       <c r="G32">
-        <v>0.0006858789009637938</v>
+        <v>0.0008172306462736407</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -2255,16 +2255,16 @@
         <v>38</v>
       </c>
       <c r="D33">
-        <v>1.001048140065421</v>
+        <v>1.001163063303462</v>
       </c>
       <c r="E33">
-        <v>0.9972383715822332</v>
+        <v>0.997341231492058</v>
       </c>
       <c r="F33">
-        <v>1.004872463078708</v>
+        <v>1.004999540451821</v>
       </c>
       <c r="G33">
-        <v>0.5902465779075889</v>
+        <v>0.5513991195818684</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
@@ -2281,16 +2281,16 @@
         <v>36</v>
       </c>
       <c r="D34">
-        <v>1.138563930257518</v>
+        <v>1.144059758762714</v>
       </c>
       <c r="E34">
-        <v>0.9377926108090953</v>
+        <v>0.9417803367668338</v>
       </c>
       <c r="F34">
-        <v>1.382318231495788</v>
+        <v>1.389785580057455</v>
       </c>
       <c r="G34">
-        <v>0.1898338650910271</v>
+        <v>0.1751873000820075</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>38</v>
       </c>
       <c r="D35">
-        <v>1.003784416922858</v>
+        <v>1.003817582945308</v>
       </c>
       <c r="E35">
-        <v>0.9995035528090305</v>
+        <v>0.9995393421902147</v>
       </c>
       <c r="F35">
-        <v>1.008083615936556</v>
+        <v>1.008114135479825</v>
       </c>
       <c r="G35">
-        <v>0.08323097823808318</v>
+        <v>0.08037349487819243</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -2333,16 +2333,16 @@
         <v>36</v>
       </c>
       <c r="D36">
-        <v>1.423269373598292</v>
+        <v>1.440749042005726</v>
       </c>
       <c r="E36">
-        <v>1.044745300229343</v>
+        <v>1.051979139750009</v>
       </c>
       <c r="F36">
-        <v>1.938937374858919</v>
+        <v>1.973192930929883</v>
       </c>
       <c r="G36">
-        <v>0.02525701657132073</v>
+        <v>0.02285977471647863</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -2359,16 +2359,16 @@
         <v>38</v>
       </c>
       <c r="D37">
-        <v>1.006152038726437</v>
+        <v>1.006256325682083</v>
       </c>
       <c r="E37">
-        <v>1.001830832363143</v>
+        <v>1.001899164535377</v>
       </c>
       <c r="F37">
-        <v>1.010491883789829</v>
+        <v>1.010632435695034</v>
       </c>
       <c r="G37">
-        <v>0.005223408932323592</v>
+        <v>0.004848567306493616</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -2385,16 +2385,16 @@
         <v>36</v>
       </c>
       <c r="D38">
-        <v>0.694245868799462</v>
+        <v>0.6950284753158306</v>
       </c>
       <c r="E38">
-        <v>0.5293974419246372</v>
+        <v>0.5297457267230347</v>
       </c>
       <c r="F38">
-        <v>0.9104262472309643</v>
+        <v>0.9118800910165855</v>
       </c>
       <c r="G38">
-        <v>0.008328675238015211</v>
+        <v>0.008645606452922982</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -2411,16 +2411,16 @@
         <v>38</v>
       </c>
       <c r="D39">
-        <v>1.000636993627791</v>
+        <v>1.000636956154756</v>
       </c>
       <c r="E39">
-        <v>0.9979307195798589</v>
+        <v>0.9979295567836879</v>
       </c>
       <c r="F39">
-        <v>1.003350606781614</v>
+        <v>1.003351700745039</v>
       </c>
       <c r="G39">
-        <v>0.6449046004215976</v>
+        <v>0.645061683191984</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>36</v>
       </c>
       <c r="D40">
-        <v>1.035427115998951</v>
+        <v>1.034176059383329</v>
       </c>
       <c r="E40">
-        <v>0.8179030947187552</v>
+        <v>0.8169190513550648</v>
       </c>
       <c r="F40">
-        <v>1.310802367014594</v>
+        <v>1.309211873596978</v>
       </c>
       <c r="G40">
-        <v>0.7723196349853156</v>
+        <v>0.780014469981629</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
@@ -2463,16 +2463,16 @@
         <v>38</v>
       </c>
       <c r="D41">
-        <v>1.007157960665007</v>
+        <v>1.007181893853036</v>
       </c>
       <c r="E41">
-        <v>1.001965451637281</v>
+        <v>1.0019772401803</v>
       </c>
       <c r="F41">
-        <v>1.012377378953884</v>
+        <v>1.012413582491006</v>
       </c>
       <c r="G41">
-        <v>0.006840843792516123</v>
+        <v>0.006784905578406887</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2489,16 +2489,16 @@
         <v>36</v>
       </c>
       <c r="D42">
-        <v>2.457233350711959</v>
+        <v>2.45765070384205</v>
       </c>
       <c r="E42">
-        <v>1.817464859614444</v>
+        <v>1.817558536324501</v>
       </c>
       <c r="F42">
-        <v>3.322207693815892</v>
+        <v>3.323165037814745</v>
       </c>
       <c r="G42">
-        <v>5.140427668395842E-09</v>
+        <v>5.177208081313466E-09</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2515,16 +2515,16 @@
         <v>38</v>
       </c>
       <c r="D43">
-        <v>1.002862104438361</v>
+        <v>1.002878581202571</v>
       </c>
       <c r="E43">
-        <v>0.9993981965729114</v>
+        <v>0.9994226209501283</v>
       </c>
       <c r="F43">
-        <v>1.006338018186692</v>
+        <v>1.006346492016283</v>
       </c>
       <c r="G43">
-        <v>0.1054554951519351</v>
+        <v>0.1026697206076568</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
@@ -2541,16 +2541,16 @@
         <v>36</v>
       </c>
       <c r="D44">
-        <v>1.015414895936822</v>
+        <v>1.017020819854886</v>
       </c>
       <c r="E44">
-        <v>0.7387097012637589</v>
+        <v>0.7382768061445404</v>
       </c>
       <c r="F44">
-        <v>1.395768065759083</v>
+        <v>1.401007507495506</v>
       </c>
       <c r="G44">
-        <v>0.9249187139414663</v>
+        <v>0.91774711062823</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
@@ -2567,16 +2567,16 @@
         <v>38</v>
       </c>
       <c r="D45">
-        <v>1.00070760594276</v>
+        <v>1.000739822349724</v>
       </c>
       <c r="E45">
-        <v>0.9970260729740655</v>
+        <v>0.9970619435822182</v>
       </c>
       <c r="F45">
-        <v>1.004402733024354</v>
+        <v>1.004431267769046</v>
       </c>
       <c r="G45">
-        <v>0.7068032616638825</v>
+        <v>0.693819931639563</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -2593,16 +2593,16 @@
         <v>36</v>
       </c>
       <c r="D46">
-        <v>1.005666651242785</v>
+        <v>1.012121315466989</v>
       </c>
       <c r="E46">
-        <v>0.8113700877685383</v>
+        <v>0.8166479139783013</v>
       </c>
       <c r="F46">
-        <v>1.246490878414526</v>
+        <v>1.25438336361176</v>
       </c>
       <c r="G46">
-        <v>0.9588566634134834</v>
+        <v>0.9123761648178338</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>38</v>
       </c>
       <c r="D47">
-        <v>1.000149796400414</v>
+        <v>1.000127721108643</v>
       </c>
       <c r="E47">
-        <v>0.996380721529692</v>
+        <v>0.9963598959843307</v>
       </c>
       <c r="F47">
-        <v>1.003933128798479</v>
+        <v>1.003909794604679</v>
       </c>
       <c r="G47">
-        <v>0.9380230434036511</v>
+        <v>0.9471250188513485</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>36</v>
       </c>
       <c r="D48">
-        <v>1.397460889535761</v>
+        <v>1.395488902305418</v>
       </c>
       <c r="E48">
-        <v>1.112821670582818</v>
+        <v>1.112143261816228</v>
       </c>
       <c r="F48">
-        <v>1.754905560707935</v>
+        <v>1.751023760443706</v>
       </c>
       <c r="G48">
-        <v>0.003978291096027964</v>
+        <v>0.004003781664126778</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2671,16 +2671,16 @@
         <v>38</v>
       </c>
       <c r="D49">
-        <v>1.008014044221147</v>
+        <v>1.008142745354075</v>
       </c>
       <c r="E49">
-        <v>1.004482700047146</v>
+        <v>1.004635235270167</v>
       </c>
       <c r="F49">
-        <v>1.011557803135267</v>
+        <v>1.011662501302508</v>
       </c>
       <c r="G49">
-        <v>8.276745773741619E-06</v>
+        <v>5.100443461499252E-06</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2697,16 +2697,16 @@
         <v>36</v>
       </c>
       <c r="D50">
-        <v>1.60152490241863</v>
+        <v>1.600990128837742</v>
       </c>
       <c r="E50">
-        <v>1.241261145149817</v>
+        <v>1.240402132041116</v>
       </c>
       <c r="F50">
-        <v>2.066351648151709</v>
+        <v>2.066401956612348</v>
       </c>
       <c r="G50">
-        <v>0.0002920278634266462</v>
+        <v>0.0003007886604986013</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2723,16 +2723,16 @@
         <v>38</v>
       </c>
       <c r="D51">
-        <v>1.003518631382172</v>
+        <v>1.003702851043582</v>
       </c>
       <c r="E51">
-        <v>0.9991180684748342</v>
+        <v>0.999312949566329</v>
       </c>
       <c r="F51">
-        <v>1.007938576337049</v>
+        <v>1.008112037005228</v>
       </c>
       <c r="G51">
-        <v>0.1172385591385685</v>
+        <v>0.09840248040743324</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
@@ -2749,16 +2749,16 @@
         <v>36</v>
       </c>
       <c r="D52">
-        <v>1.266914829372377</v>
+        <v>1.266901159897615</v>
       </c>
       <c r="E52">
-        <v>0.7962283092599712</v>
+        <v>0.7962025697082546</v>
       </c>
       <c r="F52">
-        <v>2.015845412951248</v>
+        <v>2.015867079577553</v>
       </c>
       <c r="G52">
-        <v>0.3180994373724906</v>
+        <v>0.3181439491819044</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
@@ -2775,16 +2775,16 @@
         <v>38</v>
       </c>
       <c r="D53">
-        <v>1.001721483730029</v>
+        <v>1.001723134104428</v>
       </c>
       <c r="E53">
-        <v>0.9976992358153298</v>
+        <v>0.9977003125074876</v>
       </c>
       <c r="F53">
-        <v>1.005759947431717</v>
+        <v>1.005762176096809</v>
       </c>
       <c r="G53">
-        <v>0.4020976543575273</v>
+        <v>0.4017135039065469</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
@@ -2801,16 +2801,16 @@
         <v>36</v>
       </c>
       <c r="D54">
-        <v>1.241534673312882</v>
+        <v>1.243105660485886</v>
       </c>
       <c r="E54">
-        <v>0.7998051230579807</v>
+        <v>0.8002279129546351</v>
       </c>
       <c r="F54">
-        <v>1.927229897133807</v>
+        <v>1.931089453536289</v>
       </c>
       <c r="G54">
-        <v>0.3348979232852828</v>
+        <v>0.3328892263676554</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
@@ -2827,16 +2827,16 @@
         <v>38</v>
       </c>
       <c r="D55">
-        <v>1.006683554039266</v>
+        <v>1.006684970589946</v>
       </c>
       <c r="E55">
-        <v>1.000714752482246</v>
+        <v>1.000715122516197</v>
       </c>
       <c r="F55">
-        <v>1.012687956742306</v>
+        <v>1.012690432281619</v>
       </c>
       <c r="G55">
-        <v>0.02813138746196116</v>
+        <v>0.02812559932757937</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2853,16 +2853,16 @@
         <v>36</v>
       </c>
       <c r="D56">
-        <v>1.039290023708119</v>
+        <v>0.8234434302029698</v>
       </c>
       <c r="E56">
-        <v>0.8019665626452709</v>
+        <v>0.5931345817662991</v>
       </c>
       <c r="F56">
-        <v>1.346843875655434</v>
+        <v>1.143179142792917</v>
       </c>
       <c r="G56">
-        <v>0.770762485464241</v>
+        <v>0.24582779569896</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
@@ -2879,16 +2879,16 @@
         <v>38</v>
       </c>
       <c r="D57">
-        <v>0.9997721398062328</v>
+        <v>1.000168813362684</v>
       </c>
       <c r="E57">
-        <v>0.9970276836001389</v>
+        <v>0.9977441493060439</v>
       </c>
       <c r="F57">
-        <v>1.002524150506541</v>
+        <v>1.002599369707234</v>
       </c>
       <c r="G57">
-        <v>0.8709237280631639</v>
+        <v>0.8915798608957223</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
@@ -2905,16 +2905,16 @@
         <v>36</v>
       </c>
       <c r="D58">
-        <v>0.7652804800699433</v>
+        <v>0.737743999046607</v>
       </c>
       <c r="E58">
-        <v>0.3063657413504082</v>
+        <v>0.2812014998817169</v>
       </c>
       <c r="F58">
-        <v>1.911617828398888</v>
+        <v>1.935502507483841</v>
       </c>
       <c r="G58">
-        <v>0.5668256036810946</v>
+        <v>0.5365324066868226</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
@@ -2931,16 +2931,16 @@
         <v>38</v>
       </c>
       <c r="D59">
-        <v>1.003438415236727</v>
+        <v>1.003544586486782</v>
       </c>
       <c r="E59">
-        <v>0.9963972881044827</v>
+        <v>0.9962624283790078</v>
       </c>
       <c r="F59">
-        <v>1.010529299099429</v>
+        <v>1.010879973367614</v>
       </c>
       <c r="G59">
-        <v>0.3393799652682962</v>
+        <v>0.3409811120832992</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
@@ -2957,16 +2957,16 @@
         <v>36</v>
       </c>
       <c r="D60">
-        <v>1.268619637311003</v>
+        <v>1.651383978719501</v>
       </c>
       <c r="E60">
-        <v>0.735317784566384</v>
+        <v>0.9111295630799848</v>
       </c>
       <c r="F60">
-        <v>2.188707818511637</v>
+        <v>2.993063945760752</v>
       </c>
       <c r="G60">
-        <v>0.3925191434974266</v>
+        <v>0.09828557744839689</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
@@ -2983,19 +2983,19 @@
         <v>38</v>
       </c>
       <c r="D61">
-        <v>1.00224695274611</v>
+        <v>1.002291502470579</v>
       </c>
       <c r="E61">
-        <v>1.000064873404088</v>
+        <v>0.999938542690842</v>
       </c>
       <c r="F61">
-        <v>1.004433793249514</v>
+        <v>1.004649999010314</v>
       </c>
       <c r="G61">
-        <v>0.04356009751976932</v>
+        <v>0.05629915629106968</v>
       </c>
       <c r="H61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -3009,19 +3009,19 @@
         <v>36</v>
       </c>
       <c r="D62">
-        <v>1.28582744329452</v>
+        <v>1.404031362708315</v>
       </c>
       <c r="E62">
-        <v>0.9863153020501906</v>
+        <v>1.016899383881381</v>
       </c>
       <c r="F62">
-        <v>1.676291760345402</v>
+        <v>1.938543870431254</v>
       </c>
       <c r="G62">
-        <v>0.0631517476714421</v>
+        <v>0.03922849375124827</v>
       </c>
       <c r="H62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -3035,16 +3035,16 @@
         <v>38</v>
       </c>
       <c r="D63">
-        <v>1.003258716520302</v>
+        <v>1.007150426020809</v>
       </c>
       <c r="E63">
-        <v>1.000026153075944</v>
+        <v>1.002526542951415</v>
       </c>
       <c r="F63">
-        <v>1.006501729157804</v>
+        <v>1.011795635502746</v>
       </c>
       <c r="G63">
-        <v>0.0481721187468114</v>
+        <v>0.002407482511004559</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -3061,16 +3061,16 @@
         <v>36</v>
       </c>
       <c r="D64">
-        <v>1.074768880054715</v>
+        <v>1.037571506105967</v>
       </c>
       <c r="E64">
-        <v>0.7974679230001555</v>
+        <v>0.7413827102595089</v>
       </c>
       <c r="F64">
-        <v>1.448494807400349</v>
+        <v>1.452090283985951</v>
       </c>
       <c r="G64">
-        <v>0.6358017186626587</v>
+        <v>0.8297137781061874</v>
       </c>
       <c r="H64" t="b">
         <v>0</v>
@@ -3087,16 +3087,16 @@
         <v>38</v>
       </c>
       <c r="D65">
-        <v>1.001253056573891</v>
+        <v>1.000842164731408</v>
       </c>
       <c r="E65">
-        <v>0.9980195388030015</v>
+        <v>0.9972295522904147</v>
       </c>
       <c r="F65">
-        <v>1.004497050730029</v>
+        <v>1.004467864398526</v>
       </c>
       <c r="G65">
-        <v>0.4479869668737951</v>
+        <v>0.648196100767885</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
@@ -3113,16 +3113,16 @@
         <v>36</v>
       </c>
       <c r="D66">
-        <v>1.033850816654738</v>
+        <v>1.038592432239617</v>
       </c>
       <c r="E66">
-        <v>0.6451432894593614</v>
+        <v>0.4730353345950044</v>
       </c>
       <c r="F66">
-        <v>1.656759868018433</v>
+        <v>2.280324875157424</v>
       </c>
       <c r="G66">
-        <v>0.8899537758349939</v>
+        <v>0.9248159731338718</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
@@ -3139,16 +3139,16 @@
         <v>38</v>
       </c>
       <c r="D67">
-        <v>1.003759793464122</v>
+        <v>1.003088138777676</v>
       </c>
       <c r="E67">
-        <v>0.9981447554285414</v>
+        <v>0.9937601035081515</v>
       </c>
       <c r="F67">
-        <v>1.009406418753925</v>
+        <v>1.012503732645782</v>
       </c>
       <c r="G67">
-        <v>0.1898029333384223</v>
+        <v>0.5177354646401926</v>
       </c>
       <c r="H67" t="b">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         <v>36</v>
       </c>
       <c r="D68">
-        <v>1.18132570316769</v>
+        <v>1.222772912643175</v>
       </c>
       <c r="E68">
-        <v>0.9169346872724226</v>
+        <v>0.9580041454740835</v>
       </c>
       <c r="F68">
-        <v>1.521951820926175</v>
+        <v>1.560717250502046</v>
       </c>
       <c r="G68">
-        <v>0.197361338503723</v>
+        <v>0.1062300238281453</v>
       </c>
       <c r="H68" t="b">
         <v>0</v>
@@ -3191,16 +3191,16 @@
         <v>38</v>
       </c>
       <c r="D69">
-        <v>1.001315097314079</v>
+        <v>0.9975776734436728</v>
       </c>
       <c r="E69">
-        <v>0.9988845941265224</v>
+        <v>0.9945170612658453</v>
       </c>
       <c r="F69">
-        <v>1.003751514443825</v>
+        <v>1.000647704612152</v>
       </c>
       <c r="G69">
-        <v>0.2891871777600647</v>
+        <v>0.1218732532373463</v>
       </c>
       <c r="H69" t="b">
         <v>0</v>
@@ -3217,16 +3217,16 @@
         <v>36</v>
       </c>
       <c r="D70">
-        <v>1.731259606347015</v>
+        <v>1.913335281357969</v>
       </c>
       <c r="E70">
-        <v>1.227707656550429</v>
+        <v>1.315304003106505</v>
       </c>
       <c r="F70">
-        <v>2.44134652787816</v>
+        <v>2.783274353490086</v>
       </c>
       <c r="G70">
-        <v>0.001749064576476962</v>
+        <v>0.0006907129534753885</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3243,16 +3243,16 @@
         <v>38</v>
       </c>
       <c r="D71">
-        <v>1.004491723350981</v>
+        <v>1.005132792492014</v>
       </c>
       <c r="E71">
-        <v>1.000565688923459</v>
+        <v>1.000599735869544</v>
       </c>
       <c r="F71">
-        <v>1.008433162810373</v>
+        <v>1.009686385400479</v>
       </c>
       <c r="G71">
-        <v>0.02489667103307695</v>
+        <v>0.02642301258550935</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3269,19 +3269,19 @@
         <v>36</v>
       </c>
       <c r="D72">
-        <v>1.439854927663557</v>
+        <v>1.6468267254479</v>
       </c>
       <c r="E72">
-        <v>0.9521943812007675</v>
+        <v>1.046497819915044</v>
       </c>
       <c r="F72">
-        <v>2.177267849556763</v>
+        <v>2.591537423240519</v>
       </c>
       <c r="G72">
-        <v>0.08402605929359047</v>
+        <v>0.03104995700538832</v>
       </c>
       <c r="H72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -3295,16 +3295,16 @@
         <v>38</v>
       </c>
       <c r="D73">
-        <v>1.0015205346393</v>
+        <v>1.003181619237968</v>
       </c>
       <c r="E73">
-        <v>0.993232668351432</v>
+        <v>0.9940300484521439</v>
       </c>
       <c r="F73">
-        <v>1.00987755766133</v>
+        <v>1.012417444265381</v>
       </c>
       <c r="G73">
-        <v>0.7200684569357514</v>
+        <v>0.4969080312190544</v>
       </c>
       <c r="H73" t="b">
         <v>0</v>
@@ -3321,16 +3321,16 @@
         <v>36</v>
       </c>
       <c r="D74">
-        <v>1.406888543048306</v>
+        <v>1.514351360999641</v>
       </c>
       <c r="E74">
-        <v>0.8477787304790452</v>
+        <v>0.8481419318709229</v>
       </c>
       <c r="F74">
-        <v>2.334731105417262</v>
+        <v>2.703863537913689</v>
       </c>
       <c r="G74">
-        <v>0.1865107491658347</v>
+        <v>0.1605918374274159</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
@@ -3347,16 +3347,16 @@
         <v>38</v>
       </c>
       <c r="D75">
-        <v>0.9978566514144245</v>
+        <v>0.996210764518184</v>
       </c>
       <c r="E75">
-        <v>0.993897163595186</v>
+        <v>0.9914165872011507</v>
       </c>
       <c r="F75">
-        <v>1.001831913042428</v>
+        <v>1.001028124961709</v>
       </c>
       <c r="G75">
-        <v>0.2901807814530868</v>
+        <v>0.1229619080731072</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
@@ -3373,16 +3373,16 @@
         <v>36</v>
       </c>
       <c r="D76">
-        <v>2.411347833256714</v>
+        <v>2.442123694777389</v>
       </c>
       <c r="E76">
-        <v>1.321057614189294</v>
+        <v>1.286947545799433</v>
       </c>
       <c r="F76">
-        <v>4.40147220719071</v>
+        <v>4.634196754995511</v>
       </c>
       <c r="G76">
-        <v>0.004145873720786432</v>
+        <v>0.006298574022959879</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3399,16 +3399,16 @@
         <v>38</v>
       </c>
       <c r="D77">
-        <v>1.01817126839501</v>
+        <v>1.021281816430741</v>
       </c>
       <c r="E77">
-        <v>1.008313153679677</v>
+        <v>1.010250087021869</v>
       </c>
       <c r="F77">
-        <v>1.028125764304405</v>
+        <v>1.032434010123967</v>
       </c>
       <c r="G77">
-        <v>0.0002859418729091099</v>
+        <v>0.0001445013238341735</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3425,16 +3425,16 @@
         <v>36</v>
       </c>
       <c r="D78">
-        <v>1.258192600310795</v>
+        <v>1.040614185823995</v>
       </c>
       <c r="E78">
-        <v>0.8933425807320131</v>
+        <v>0.7215342889811778</v>
       </c>
       <c r="F78">
-        <v>1.772051006658248</v>
+        <v>1.500798922899676</v>
       </c>
       <c r="G78">
-        <v>0.1886861729682803</v>
+        <v>0.831261771012374</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
@@ -3451,16 +3451,16 @@
         <v>38</v>
       </c>
       <c r="D79">
-        <v>1.003009578491328</v>
+        <v>1.006471249109684</v>
       </c>
       <c r="E79">
-        <v>0.9929250283743057</v>
+        <v>0.9956922282109009</v>
       </c>
       <c r="F79">
-        <v>1.013196551397742</v>
+        <v>1.017366959973744</v>
       </c>
       <c r="G79">
-        <v>0.5599939666016891</v>
+        <v>0.2403379628366893</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
@@ -3477,16 +3477,16 @@
         <v>36</v>
       </c>
       <c r="D80">
-        <v>1.682585525333173</v>
+        <v>1.762916087335205</v>
       </c>
       <c r="E80">
-        <v>1.161346666102117</v>
+        <v>1.200400603992228</v>
       </c>
       <c r="F80">
-        <v>2.437768267388106</v>
+        <v>2.589029962705176</v>
       </c>
       <c r="G80">
-        <v>0.00594654094248549</v>
+        <v>0.003834216225811201</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3503,16 +3503,16 @@
         <v>38</v>
       </c>
       <c r="D81">
-        <v>1.002920865788964</v>
+        <v>1.003293449111411</v>
       </c>
       <c r="E81">
-        <v>0.9961829466307492</v>
+        <v>0.9962023648061871</v>
       </c>
       <c r="F81">
-        <v>1.009704358458285</v>
+        <v>1.010435008579514</v>
       </c>
       <c r="G81">
-        <v>0.3964289835929716</v>
+        <v>0.3635743799683276</v>
       </c>
       <c r="H81" t="b">
         <v>0</v>
@@ -3529,19 +3529,19 @@
         <v>36</v>
       </c>
       <c r="D82">
-        <v>0.5952736812823629</v>
+        <v>0.2176025726242568</v>
       </c>
       <c r="E82">
-        <v>0.3332402633448189</v>
+        <v>0.118161058651417</v>
       </c>
       <c r="F82">
-        <v>1.063349164565967</v>
+        <v>0.4007316805816985</v>
       </c>
       <c r="G82">
-        <v>0.07969559543311983</v>
+        <v>9.820905816488161E-07</v>
       </c>
       <c r="H82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -3555,16 +3555,16 @@
         <v>38</v>
       </c>
       <c r="D83">
-        <v>0.9991665256887716</v>
+        <v>0.9929916995924484</v>
       </c>
       <c r="E83">
-        <v>0.9931825129207854</v>
+        <v>0.9855042022110498</v>
       </c>
       <c r="F83">
-        <v>1.005186592664662</v>
+        <v>1.000536084216855</v>
       </c>
       <c r="G83">
-        <v>0.7855767150495655</v>
+        <v>0.06857910043430827</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
@@ -3581,16 +3581,16 @@
         <v>36</v>
       </c>
       <c r="D84">
-        <v>0.5968248106130553</v>
+        <v>0.3773424672244965</v>
       </c>
       <c r="E84">
-        <v>0.4088521520594369</v>
+        <v>0.211677667091154</v>
       </c>
       <c r="F84">
-        <v>0.8712192237929732</v>
+        <v>0.6726611244716454</v>
       </c>
       <c r="G84">
-        <v>0.007489017734945024</v>
+        <v>0.0009520965417053778</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3607,16 +3607,16 @@
         <v>38</v>
       </c>
       <c r="D85">
-        <v>1.000832802991341</v>
+        <v>0.996923440829481</v>
       </c>
       <c r="E85">
-        <v>0.995181220315742</v>
+        <v>0.9900204050373422</v>
       </c>
       <c r="F85">
-        <v>1.006516480712634</v>
+        <v>1.003874608865062</v>
       </c>
       <c r="G85">
-        <v>0.7732556301852335</v>
+        <v>0.3847636924636354</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
@@ -3633,16 +3633,16 @@
         <v>36</v>
       </c>
       <c r="D86">
-        <v>0.9562474875324336</v>
+        <v>0.9189999623327492</v>
       </c>
       <c r="E86">
-        <v>0.7480625795495331</v>
+        <v>0.69433403336582</v>
       </c>
       <c r="F86">
-        <v>1.222370002737911</v>
+        <v>1.216361131937522</v>
       </c>
       <c r="G86">
-        <v>0.7209953452697619</v>
+        <v>0.5548076808382982</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
@@ -3659,16 +3659,16 @@
         <v>38</v>
       </c>
       <c r="D87">
-        <v>1.001277466662224</v>
+        <v>1.000784448576661</v>
       </c>
       <c r="E87">
-        <v>0.9976976484644537</v>
+        <v>0.9969212089164433</v>
       </c>
       <c r="F87">
-        <v>1.004870129531272</v>
+        <v>1.004662658949247</v>
       </c>
       <c r="G87">
-        <v>0.4847942098771651</v>
+        <v>0.691096982172283</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
@@ -3685,16 +3685,16 @@
         <v>36</v>
       </c>
       <c r="D88">
-        <v>1.326280136915186</v>
+        <v>1.584940539601711</v>
       </c>
       <c r="E88">
-        <v>1.047470624868235</v>
+        <v>1.205600459963974</v>
       </c>
       <c r="F88">
-        <v>1.679301509574111</v>
+        <v>2.083639312934593</v>
       </c>
       <c r="G88">
-        <v>0.01902028417780025</v>
+        <v>0.0009683964907444767</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3711,16 +3711,16 @@
         <v>38</v>
       </c>
       <c r="D89">
-        <v>1.003206143546407</v>
+        <v>1.004698209612346</v>
       </c>
       <c r="E89">
-        <v>0.9978287271198016</v>
+        <v>0.9981492809307255</v>
       </c>
       <c r="F89">
-        <v>1.008612539502904</v>
+        <v>1.01129010628252</v>
       </c>
       <c r="G89">
-        <v>0.24308572566969</v>
+        <v>0.160086680108217</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
@@ -3737,16 +3737,16 @@
         <v>36</v>
       </c>
       <c r="D90">
-        <v>0.7806634917377068</v>
+        <v>0.7726206071713076</v>
       </c>
       <c r="E90">
-        <v>0.4886712921580266</v>
+        <v>0.4671912241435859</v>
       </c>
       <c r="F90">
-        <v>1.24712766457136</v>
+        <v>1.27772648923366</v>
       </c>
       <c r="G90">
-        <v>0.3002117613591552</v>
+        <v>0.314857018558248</v>
       </c>
       <c r="H90" t="b">
         <v>0</v>
@@ -3763,16 +3763,16 @@
         <v>38</v>
       </c>
       <c r="D91">
-        <v>0.996513952960195</v>
+        <v>0.9959497871946362</v>
       </c>
       <c r="E91">
-        <v>0.9893671313569341</v>
+        <v>0.9882906562465208</v>
       </c>
       <c r="F91">
-        <v>1.00371240055487</v>
+        <v>1.003668275464922</v>
       </c>
       <c r="G91">
-        <v>0.3416406899787507</v>
+        <v>0.3028404046445279</v>
       </c>
       <c r="H91" t="b">
         <v>0</v>
@@ -3789,16 +3789,16 @@
         <v>36</v>
       </c>
       <c r="D92">
-        <v>0.9924344623513331</v>
+        <v>0.9409396696780898</v>
       </c>
       <c r="E92">
-        <v>0.733781584687263</v>
+        <v>0.6690054033307924</v>
       </c>
       <c r="F92">
-        <v>1.342260670772154</v>
+        <v>1.32340853686071</v>
       </c>
       <c r="G92">
-        <v>0.9606843260914301</v>
+        <v>0.726482037406841</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
@@ -3815,16 +3815,16 @@
         <v>38</v>
       </c>
       <c r="D93">
-        <v>0.9996044690809768</v>
+        <v>0.9990251345556173</v>
       </c>
       <c r="E93">
-        <v>0.9966241575433694</v>
+        <v>0.9958633743676695</v>
       </c>
       <c r="F93">
-        <v>1.002593692962113</v>
+        <v>1.002196932995542</v>
       </c>
       <c r="G93">
-        <v>0.7951132843959654</v>
+        <v>0.5464656693179402</v>
       </c>
       <c r="H93" t="b">
         <v>0</v>
@@ -3841,16 +3841,16 @@
         <v>36</v>
       </c>
       <c r="D94">
-        <v>0.9855163625920415</v>
+        <v>1.014398883150489</v>
       </c>
       <c r="E94">
-        <v>0.9050905887990467</v>
+        <v>0.9186964231259488</v>
       </c>
       <c r="F94">
-        <v>1.073088719467714</v>
+        <v>1.120070861531904</v>
       </c>
       <c r="G94">
-        <v>0.7369498985069054</v>
+        <v>0.777362904189611</v>
       </c>
       <c r="H94" t="b">
         <v>0</v>
@@ -3867,16 +3867,16 @@
         <v>38</v>
       </c>
       <c r="D95">
-        <v>1.000650632404507</v>
+        <v>1.000768382351946</v>
       </c>
       <c r="E95">
-        <v>0.9987874762692782</v>
+        <v>0.9987770129174256</v>
       </c>
       <c r="F95">
-        <v>1.002517264104725</v>
+        <v>1.002763722194449</v>
       </c>
       <c r="G95">
-        <v>0.4939602208641379</v>
+        <v>0.4497679913650631</v>
       </c>
       <c r="H95" t="b">
         <v>0</v>
@@ -3893,16 +3893,16 @@
         <v>36</v>
       </c>
       <c r="D96">
-        <v>1.251149613049841</v>
+        <v>1.248069982410195</v>
       </c>
       <c r="E96">
-        <v>0.7560456321153276</v>
+        <v>0.7069031129992214</v>
       </c>
       <c r="F96">
-        <v>2.070477346526069</v>
+        <v>2.20352499847472</v>
       </c>
       <c r="G96">
-        <v>0.3833011060439889</v>
+        <v>0.4448448837497589</v>
       </c>
       <c r="H96" t="b">
         <v>0</v>
@@ -3919,16 +3919,16 @@
         <v>38</v>
       </c>
       <c r="D97">
-        <v>1.002842305621698</v>
+        <v>1.003423639333998</v>
       </c>
       <c r="E97">
-        <v>0.9965836223924996</v>
+        <v>0.9959558532191563</v>
       </c>
       <c r="F97">
-        <v>1.009140294248741</v>
+        <v>1.010947419727379</v>
       </c>
       <c r="G97">
-        <v>0.3742323677894542</v>
+        <v>0.3698592935080551</v>
       </c>
       <c r="H97" t="b">
         <v>0</v>
@@ -3945,16 +3945,16 @@
         <v>36</v>
       </c>
       <c r="D98">
-        <v>1.290885179130996</v>
+        <v>1.021512587835749</v>
       </c>
       <c r="E98">
-        <v>0.9660934467664687</v>
+        <v>0.6549698060934924</v>
       </c>
       <c r="F98">
-        <v>1.724868905050005</v>
+        <v>1.59318484210849</v>
       </c>
       <c r="G98">
-        <v>0.08422351247494154</v>
+        <v>0.9252192286277108</v>
       </c>
       <c r="H98" t="b">
         <v>0</v>
@@ -3971,16 +3971,16 @@
         <v>38</v>
       </c>
       <c r="D99">
-        <v>0.9948010784514612</v>
+        <v>0.9936440387742143</v>
       </c>
       <c r="E99">
-        <v>0.990384145072446</v>
+        <v>0.9884864023902943</v>
       </c>
       <c r="F99">
-        <v>0.9992377105509896</v>
+        <v>0.9988285862142745</v>
       </c>
       <c r="G99">
-        <v>0.02168485174147801</v>
+        <v>0.01633266811212109</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -3997,16 +3997,16 @@
         <v>36</v>
       </c>
       <c r="D100">
-        <v>0.549679815399025</v>
+        <v>0.2986877813344146</v>
       </c>
       <c r="E100">
-        <v>0.4230501008552867</v>
+        <v>0.210669765425111</v>
       </c>
       <c r="F100">
-        <v>0.7142130420161803</v>
+        <v>0.4234798028015514</v>
       </c>
       <c r="G100">
-        <v>7.489292794447667E-06</v>
+        <v>1.169090253718542E-11</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4023,16 +4023,16 @@
         <v>38</v>
       </c>
       <c r="D101">
-        <v>0.9947496826679273</v>
+        <v>0.9915282368920476</v>
       </c>
       <c r="E101">
-        <v>0.9916585778718816</v>
+        <v>0.9870020009511259</v>
       </c>
       <c r="F101">
-        <v>0.9978504227649458</v>
+        <v>0.9960752294391091</v>
       </c>
       <c r="G101">
-        <v>0.0009160023471972462</v>
+        <v>0.0002678698631123622</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4049,19 +4049,19 @@
         <v>36</v>
       </c>
       <c r="D102">
-        <v>1.10234236464664</v>
+        <v>1.082511760728971</v>
       </c>
       <c r="E102">
-        <v>1.001260648791173</v>
+        <v>0.9385320194631804</v>
       </c>
       <c r="F102">
-        <v>1.213628729304215</v>
+        <v>1.248579364172145</v>
       </c>
       <c r="G102">
-        <v>0.04707352470716907</v>
+        <v>0.2762489606208858</v>
       </c>
       <c r="H102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -4075,16 +4075,16 @@
         <v>38</v>
       </c>
       <c r="D103">
-        <v>0.999880968669644</v>
+        <v>0.9996028033867647</v>
       </c>
       <c r="E103">
-        <v>0.9980907212796791</v>
+        <v>0.9972708603374986</v>
       </c>
       <c r="F103">
-        <v>1.001674427176243</v>
+        <v>1.001940199275978</v>
       </c>
       <c r="G103">
-        <v>0.8964152121406583</v>
+        <v>0.7388458323492734</v>
       </c>
       <c r="H103" t="b">
         <v>0</v>
@@ -4101,16 +4101,16 @@
         <v>36</v>
       </c>
       <c r="D104">
-        <v>1.40935950687995</v>
+        <v>1.384440813380027</v>
       </c>
       <c r="E104">
-        <v>1.120391408328518</v>
+        <v>1.041562633138535</v>
       </c>
       <c r="F104">
-        <v>1.77285741828045</v>
+        <v>1.840193095231192</v>
       </c>
       <c r="G104">
-        <v>0.003379025709224402</v>
+        <v>0.02506290822823781</v>
       </c>
       <c r="H104" t="b">
         <v>1</v>
@@ -4127,16 +4127,16 @@
         <v>38</v>
       </c>
       <c r="D105">
-        <v>0.9989555891906766</v>
+        <v>0.9971469817776851</v>
       </c>
       <c r="E105">
-        <v>0.994079775888432</v>
+        <v>0.9908808003203201</v>
       </c>
       <c r="F105">
-        <v>1.003855317631258</v>
+        <v>1.003452789626079</v>
       </c>
       <c r="G105">
-        <v>0.6755196283550629</v>
+        <v>0.3743779858005316</v>
       </c>
       <c r="H105" t="b">
         <v>0</v>
@@ -4153,16 +4153,16 @@
         <v>36</v>
       </c>
       <c r="D106">
-        <v>0.9681856441634763</v>
+        <v>0.7805470290308887</v>
       </c>
       <c r="E106">
-        <v>0.5370235022698593</v>
+        <v>0.3051158475465124</v>
       </c>
       <c r="F106">
-        <v>1.745516607005407</v>
+        <v>1.996794559928819</v>
       </c>
       <c r="G106">
-        <v>0.9143790375863374</v>
+        <v>0.6051700207368469</v>
       </c>
       <c r="H106" t="b">
         <v>0</v>
@@ -4179,16 +4179,16 @@
         <v>38</v>
       </c>
       <c r="D107">
-        <v>0.9992621813235291</v>
+        <v>0.9974341444440007</v>
       </c>
       <c r="E107">
-        <v>0.9952574100677445</v>
+        <v>0.9921816023260404</v>
       </c>
       <c r="F107">
-        <v>1.003283067197149</v>
+        <v>1.002714493163733</v>
       </c>
       <c r="G107">
-        <v>0.7186700967594031</v>
+        <v>0.3402411473914247</v>
       </c>
       <c r="H107" t="b">
         <v>0</v>
@@ -4205,16 +4205,16 @@
         <v>36</v>
       </c>
       <c r="D108">
-        <v>0.5952608127988548</v>
+        <v>0.372338864408494</v>
       </c>
       <c r="E108">
-        <v>0.392028550127741</v>
+        <v>0.2141347559578605</v>
       </c>
       <c r="F108">
-        <v>0.9038510974226096</v>
+        <v>0.6474251661243121</v>
       </c>
       <c r="G108">
-        <v>0.01491860108808649</v>
+        <v>0.0004647780613327123</v>
       </c>
       <c r="H108" t="b">
         <v>1</v>
@@ -4231,16 +4231,16 @@
         <v>38</v>
       </c>
       <c r="D109">
-        <v>0.9976706173573175</v>
+        <v>0.994821270827314</v>
       </c>
       <c r="E109">
-        <v>0.9936559216684984</v>
+        <v>0.9889979418414715</v>
       </c>
       <c r="F109">
-        <v>1.001701533732918</v>
+        <v>1.000678888216643</v>
       </c>
       <c r="G109">
-        <v>0.2569682164632652</v>
+        <v>0.08302530494175617</v>
       </c>
       <c r="H109" t="b">
         <v>0</v>
@@ -4257,16 +4257,16 @@
         <v>36</v>
       </c>
       <c r="D110">
-        <v>1.213346736671873</v>
+        <v>0.8917804150414311</v>
       </c>
       <c r="E110">
-        <v>0.9826923917037724</v>
+        <v>0.6217633213697589</v>
       </c>
       <c r="F110">
-        <v>1.49813951529613</v>
+        <v>1.27905954133715</v>
       </c>
       <c r="G110">
-        <v>0.07223003877795961</v>
+        <v>0.5336604522603494</v>
       </c>
       <c r="H110" t="b">
         <v>0</v>
@@ -4283,16 +4283,16 @@
         <v>38</v>
       </c>
       <c r="D111">
-        <v>0.9993139657351218</v>
+        <v>1.000159633348898</v>
       </c>
       <c r="E111">
-        <v>0.9957724703113625</v>
+        <v>0.9961666664549719</v>
       </c>
       <c r="F111">
-        <v>1.002868056596303</v>
+        <v>1.004168605380471</v>
       </c>
       <c r="G111">
-        <v>0.7047861695540911</v>
+        <v>0.9376638706960023</v>
       </c>
       <c r="H111" t="b">
         <v>0</v>
@@ -4309,16 +4309,16 @@
         <v>36</v>
       </c>
       <c r="D112">
-        <v>0.9996152166547333</v>
+        <v>0.9802494851461158</v>
       </c>
       <c r="E112">
-        <v>0.5034054865726275</v>
+        <v>0.4365079632020236</v>
       </c>
       <c r="F112">
-        <v>1.984941777593296</v>
+        <v>2.201309332550501</v>
       </c>
       <c r="G112">
-        <v>0.9991226356872251</v>
+        <v>0.9614545393241158</v>
       </c>
       <c r="H112" t="b">
         <v>0</v>
@@ -4335,16 +4335,16 @@
         <v>38</v>
       </c>
       <c r="D113">
-        <v>0.9999589772242442</v>
+        <v>0.999439549326437</v>
       </c>
       <c r="E113">
-        <v>0.9933597763696077</v>
+        <v>0.9915969681765177</v>
       </c>
       <c r="F113">
-        <v>1.006602018641944</v>
+        <v>1.007344157772795</v>
       </c>
       <c r="G113">
-        <v>0.9903113056847598</v>
+        <v>0.889075112509997</v>
       </c>
       <c r="H113" t="b">
         <v>0</v>
@@ -4361,16 +4361,16 @@
         <v>36</v>
       </c>
       <c r="D114">
-        <v>1.077586162158778</v>
+        <v>2.040134880908046</v>
       </c>
       <c r="E114">
-        <v>0.6011288085936366</v>
+        <v>0.8023035822766105</v>
       </c>
       <c r="F114">
-        <v>1.931685722387414</v>
+        <v>5.187749904452878</v>
       </c>
       <c r="G114">
-        <v>0.8018746168133486</v>
+        <v>0.1342931462286086</v>
       </c>
       <c r="H114" t="b">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>38</v>
       </c>
       <c r="D115">
-        <v>1.001077105201586</v>
+        <v>1.002179254895729</v>
       </c>
       <c r="E115">
-        <v>0.9981951274852465</v>
+        <v>0.99824819968226</v>
       </c>
       <c r="F115">
-        <v>1.003967403731491</v>
+        <v>1.006125790422708</v>
       </c>
       <c r="G115">
-        <v>0.464258716983076</v>
+        <v>0.2776597565432629</v>
       </c>
       <c r="H115" t="b">
         <v>0</v>
@@ -4413,16 +4413,16 @@
         <v>36</v>
       </c>
       <c r="D116">
-        <v>1.524721492968052</v>
+        <v>1.524754572927611</v>
       </c>
       <c r="E116">
-        <v>0.8277071794231586</v>
+        <v>0.7522885934007699</v>
       </c>
       <c r="F116">
-        <v>2.808693326471925</v>
+        <v>3.090405102586899</v>
       </c>
       <c r="G116">
-        <v>0.175962625257669</v>
+        <v>0.2418813745021179</v>
       </c>
       <c r="H116" t="b">
         <v>0</v>
@@ -4439,16 +4439,16 @@
         <v>38</v>
       </c>
       <c r="D117">
-        <v>1.000225618495207</v>
+        <v>1.001260651358986</v>
       </c>
       <c r="E117">
-        <v>0.9939350354838096</v>
+        <v>0.994671888744306</v>
       </c>
       <c r="F117">
-        <v>1.006556014405044</v>
+        <v>1.00789305830833</v>
       </c>
       <c r="G117">
-        <v>0.9441277353401415</v>
+        <v>0.7083989941380364</v>
       </c>
       <c r="H117" t="b">
         <v>0</v>
@@ -4465,16 +4465,16 @@
         <v>36</v>
       </c>
       <c r="D118">
-        <v>1.342592404629737</v>
+        <v>1.404078847605094</v>
       </c>
       <c r="E118">
-        <v>0.8133030112494565</v>
+        <v>0.6311127921483265</v>
       </c>
       <c r="F118">
-        <v>2.216337994618071</v>
+        <v>3.123748139506441</v>
       </c>
       <c r="G118">
-        <v>0.249349320543014</v>
+        <v>0.4055043416947236</v>
       </c>
       <c r="H118" t="b">
         <v>0</v>
@@ -4491,16 +4491,16 @@
         <v>38</v>
       </c>
       <c r="D119">
-        <v>1.001657853288355</v>
+        <v>0.9997849331544632</v>
       </c>
       <c r="E119">
-        <v>0.995859787852086</v>
+        <v>0.9911452117880892</v>
       </c>
       <c r="F119">
-        <v>1.007489676049916</v>
+        <v>1.008499966174872</v>
       </c>
       <c r="G119">
-        <v>0.5759869494114294</v>
+        <v>0.9612598639255336</v>
       </c>
       <c r="H119" t="b">
         <v>0</v>
@@ -4517,19 +4517,19 @@
         <v>36</v>
       </c>
       <c r="D120">
-        <v>1.36064236700618</v>
+        <v>1.433493247222863</v>
       </c>
       <c r="E120">
-        <v>1.061163241212558</v>
+        <v>0.8380964569893981</v>
       </c>
       <c r="F120">
-        <v>1.744639824478563</v>
+        <v>2.451869200372412</v>
       </c>
       <c r="G120">
-        <v>0.01518150123499625</v>
+        <v>0.1885082030495785</v>
       </c>
       <c r="H120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -4543,19 +4543,19 @@
         <v>38</v>
       </c>
       <c r="D121">
-        <v>0.9991230590222409</v>
+        <v>0.9913174362662867</v>
       </c>
       <c r="E121">
-        <v>0.9956282599568687</v>
+        <v>0.9846298320986244</v>
       </c>
       <c r="F121">
-        <v>1.002630125337347</v>
+        <v>0.9980504626302357</v>
       </c>
       <c r="G121">
-        <v>0.6236154656900822</v>
+        <v>0.01156981426021445</v>
       </c>
       <c r="H121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -4569,16 +4569,16 @@
         <v>36</v>
       </c>
       <c r="D122">
-        <v>0.9397616861270327</v>
+        <v>1.484017714066521</v>
       </c>
       <c r="E122">
-        <v>0.5572577758772063</v>
+        <v>0.8112796371051259</v>
       </c>
       <c r="F122">
-        <v>1.584817771850938</v>
+        <v>2.714610936768584</v>
       </c>
       <c r="G122">
-        <v>0.8157538259627399</v>
+        <v>0.2001287581824394</v>
       </c>
       <c r="H122" t="b">
         <v>0</v>
@@ -4595,16 +4595,16 @@
         <v>38</v>
       </c>
       <c r="D123">
-        <v>1.00341537754511</v>
+        <v>0.9996006420189333</v>
       </c>
       <c r="E123">
-        <v>0.9980970325415207</v>
+        <v>0.9947181149990388</v>
       </c>
       <c r="F123">
-        <v>1.008762061269941</v>
+        <v>1.004507134692756</v>
       </c>
       <c r="G123">
-        <v>0.2085841733916918</v>
+        <v>0.8729691918380911</v>
       </c>
       <c r="H123" t="b">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>36</v>
       </c>
       <c r="D124">
-        <v>1.780577372630619</v>
+        <v>1.320469216258964</v>
       </c>
       <c r="E124">
-        <v>1.122195202160349</v>
+        <v>0.8139857248592474</v>
       </c>
       <c r="F124">
-        <v>2.825226639554939</v>
+        <v>2.142100159544037</v>
       </c>
       <c r="G124">
-        <v>0.01430864052065379</v>
+        <v>0.2600898967564158</v>
       </c>
       <c r="H124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -4647,16 +4647,16 @@
         <v>38</v>
       </c>
       <c r="D125">
-        <v>1.003086761531009</v>
+        <v>0.9976769243147309</v>
       </c>
       <c r="E125">
-        <v>0.9978701691783579</v>
+        <v>0.9930893483225632</v>
       </c>
       <c r="F125">
-        <v>1.008330624801876</v>
+        <v>1.002285692613028</v>
       </c>
       <c r="G125">
-        <v>0.2466539899027891</v>
+        <v>0.3226337988739168</v>
       </c>
       <c r="H125" t="b">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>36</v>
       </c>
       <c r="D126">
-        <v>0.8733024929944135</v>
+        <v>0.580145933840621</v>
       </c>
       <c r="E126">
-        <v>0.5968104378429989</v>
+        <v>0.3352452286415158</v>
       </c>
       <c r="F126">
-        <v>1.277888582221626</v>
+        <v>1.003949574213646</v>
       </c>
       <c r="G126">
-        <v>0.4854952862506095</v>
+        <v>0.05166956655998836</v>
       </c>
       <c r="H126" t="b">
         <v>0</v>
@@ -4699,16 +4699,16 @@
         <v>38</v>
       </c>
       <c r="D127">
-        <v>0.9920002770713133</v>
+        <v>0.9843444139317051</v>
       </c>
       <c r="E127">
-        <v>0.9854654275591588</v>
+        <v>0.9765532951679755</v>
       </c>
       <c r="F127">
-        <v>0.9985784606842412</v>
+        <v>0.9921976916496781</v>
       </c>
       <c r="G127">
-        <v>0.01722761667305362</v>
+        <v>9.946027333434123E-05</v>
       </c>
       <c r="H127" t="b">
         <v>1</v>
@@ -4725,19 +4725,19 @@
         <v>36</v>
       </c>
       <c r="D128">
-        <v>1.587542250387942</v>
+        <v>2.501912402849681</v>
       </c>
       <c r="E128">
-        <v>0.9237735383436404</v>
+        <v>1.410088951257375</v>
       </c>
       <c r="F128">
-        <v>2.728255673231107</v>
+        <v>4.439128230847718</v>
       </c>
       <c r="G128">
-        <v>0.09433395926320273</v>
+        <v>0.001720806826475694</v>
       </c>
       <c r="H128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -4751,19 +4751,19 @@
         <v>38</v>
       </c>
       <c r="D129">
-        <v>0.9992509608897834</v>
+        <v>0.9936352859188957</v>
       </c>
       <c r="E129">
-        <v>0.9938824987249374</v>
+        <v>0.9884920094194855</v>
       </c>
       <c r="F129">
-        <v>1.0046484208346</v>
+        <v>0.9988053236798006</v>
       </c>
       <c r="G129">
-        <v>0.7851390568772526</v>
+        <v>0.01589039477756067</v>
       </c>
       <c r="H129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -4777,16 +4777,16 @@
         <v>36</v>
       </c>
       <c r="D130">
-        <v>1.345395470509055</v>
+        <v>1.180638320235772</v>
       </c>
       <c r="E130">
-        <v>0.9506921305978661</v>
+        <v>0.7647140279199474</v>
       </c>
       <c r="F130">
-        <v>1.90396965937644</v>
+        <v>1.822781840422918</v>
       </c>
       <c r="G130">
-        <v>0.09401957004356207</v>
+        <v>0.4536280188507365</v>
       </c>
       <c r="H130" t="b">
         <v>0</v>
@@ -4803,16 +4803,16 @@
         <v>38</v>
       </c>
       <c r="D131">
-        <v>1.000514176375199</v>
+        <v>0.9985077983281346</v>
       </c>
       <c r="E131">
-        <v>0.9906444932945755</v>
+        <v>0.9865249321972771</v>
       </c>
       <c r="F131">
-        <v>1.010482190032302</v>
+        <v>1.010636214840968</v>
       </c>
       <c r="G131">
-        <v>0.9190511528847677</v>
+        <v>0.8084534028064513</v>
       </c>
       <c r="H131" t="b">
         <v>0</v>
@@ -4829,16 +4829,16 @@
         <v>36</v>
       </c>
       <c r="D132">
-        <v>0.9972242000920767</v>
+        <v>0.8704084291605779</v>
       </c>
       <c r="E132">
-        <v>0.854111915842195</v>
+        <v>0.7383493249461947</v>
       </c>
       <c r="F132">
-        <v>1.164315924885208</v>
+        <v>1.026087257016174</v>
       </c>
       <c r="G132">
-        <v>0.9719455793094546</v>
+        <v>0.09828757405552212</v>
       </c>
       <c r="H132" t="b">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>38</v>
       </c>
       <c r="D133">
-        <v>1.004929555296167</v>
+        <v>1.01022866016689</v>
       </c>
       <c r="E133">
-        <v>0.9995043083566105</v>
+        <v>1.003663029800558</v>
       </c>
       <c r="F133">
-        <v>1.010384250137157</v>
+        <v>1.016837240707561</v>
       </c>
       <c r="G133">
-        <v>0.07500303642725785</v>
+        <v>0.002220573418480827</v>
       </c>
       <c r="H133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -4881,16 +4881,16 @@
         <v>36</v>
       </c>
       <c r="D134">
-        <v>1.513699453304582</v>
+        <v>1.845503316472165</v>
       </c>
       <c r="E134">
-        <v>1.008526248772859</v>
+        <v>1.006398147763925</v>
       </c>
       <c r="F134">
-        <v>2.271915121418554</v>
+        <v>3.384229689489346</v>
       </c>
       <c r="G134">
-        <v>0.04539850766809601</v>
+        <v>0.04763854704919675</v>
       </c>
       <c r="H134" t="b">
         <v>1</v>
@@ -4907,16 +4907,16 @@
         <v>38</v>
       </c>
       <c r="D135">
-        <v>1.00150649113376</v>
+        <v>1.002918625920145</v>
       </c>
       <c r="E135">
-        <v>0.9969202703422979</v>
+        <v>0.9964781792340798</v>
       </c>
       <c r="F135">
-        <v>1.006113810323734</v>
+        <v>1.009400698558871</v>
       </c>
       <c r="G135">
-        <v>0.5203400537595522</v>
+        <v>0.3752752686830715</v>
       </c>
       <c r="H135" t="b">
         <v>0</v>
@@ -4933,16 +4933,16 @@
         <v>36</v>
       </c>
       <c r="D136">
-        <v>1.570972047125325</v>
+        <v>1.426083878994242</v>
       </c>
       <c r="E136">
-        <v>0.8246827092325142</v>
+        <v>0.33182491133338</v>
       </c>
       <c r="F136">
-        <v>2.992609333528916</v>
+        <v>6.128880504345313</v>
       </c>
       <c r="G136">
-        <v>0.1695239612221022</v>
+        <v>0.6332888331756688</v>
       </c>
       <c r="H136" t="b">
         <v>0</v>
@@ -4959,16 +4959,16 @@
         <v>38</v>
       </c>
       <c r="D137">
-        <v>0.996195510753197</v>
+        <v>0.9899706099145681</v>
       </c>
       <c r="E137">
-        <v>0.990580948028385</v>
+        <v>0.9771946831476868</v>
       </c>
       <c r="F137">
-        <v>1.001841896535633</v>
+        <v>1.002913570239417</v>
       </c>
       <c r="G137">
-        <v>0.1862265805348489</v>
+        <v>0.1282662104453955</v>
       </c>
       <c r="H137" t="b">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         <v>36</v>
       </c>
       <c r="D138">
-        <v>0.5471947100177307</v>
+        <v>0.3889996507540542</v>
       </c>
       <c r="E138">
-        <v>0.3195606975898098</v>
+        <v>0.2059968617684318</v>
       </c>
       <c r="F138">
-        <v>0.9369802135546983</v>
+        <v>0.7345778328258276</v>
       </c>
       <c r="G138">
-        <v>0.02800868796189254</v>
+        <v>0.003603122672916738</v>
       </c>
       <c r="H138" t="b">
         <v>1</v>
@@ -5011,19 +5011,19 @@
         <v>38</v>
       </c>
       <c r="D139">
-        <v>0.9985527588557657</v>
+        <v>0.9889617119166448</v>
       </c>
       <c r="E139">
-        <v>0.9919937674154793</v>
+        <v>0.9825888722848624</v>
       </c>
       <c r="F139">
-        <v>1.005155117875695</v>
+        <v>0.9953758842829188</v>
       </c>
       <c r="G139">
-        <v>0.6666632412937168</v>
+        <v>0.0007650883444557331</v>
       </c>
       <c r="H139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -5037,16 +5037,16 @@
         <v>36</v>
       </c>
       <c r="D140">
-        <v>0.9841832465543681</v>
+        <v>1.026310268924579</v>
       </c>
       <c r="E140">
-        <v>0.7921447867843068</v>
+        <v>0.7729010747810605</v>
       </c>
       <c r="F140">
-        <v>1.222777298996529</v>
+        <v>1.362804118752732</v>
       </c>
       <c r="G140">
-        <v>0.8855358850480041</v>
+        <v>0.8575482060369555</v>
       </c>
       <c r="H140" t="b">
         <v>0</v>
@@ -5063,19 +5063,19 @@
         <v>38</v>
       </c>
       <c r="D141">
-        <v>1.004179845538464</v>
+        <v>1.007995284023513</v>
       </c>
       <c r="E141">
-        <v>0.9990509426110595</v>
+        <v>1.000781586801849</v>
       </c>
       <c r="F141">
-        <v>1.009335079100391</v>
+        <v>1.015260978032779</v>
       </c>
       <c r="G141">
-        <v>0.1103699083684645</v>
+        <v>0.02976759435018484</v>
       </c>
       <c r="H141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -5089,16 +5089,16 @@
         <v>36</v>
       </c>
       <c r="D142">
-        <v>1.036772261939577</v>
+        <v>1.136308704007964</v>
       </c>
       <c r="E142">
-        <v>0.8522727378550229</v>
+        <v>0.9234741951436904</v>
       </c>
       <c r="F142">
-        <v>1.261212139476124</v>
+        <v>1.398195507350751</v>
       </c>
       <c r="G142">
-        <v>0.7179587662257509</v>
+        <v>0.2271995018550084</v>
       </c>
       <c r="H142" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>38</v>
       </c>
       <c r="D143">
-        <v>1.002122531178833</v>
+        <v>1.003185449741712</v>
       </c>
       <c r="E143">
-        <v>0.9980610908372125</v>
+        <v>0.9984640260508413</v>
       </c>
       <c r="F143">
-        <v>1.006200498863118</v>
+        <v>1.007929199566612</v>
       </c>
       <c r="G143">
-        <v>0.3061683661870696</v>
+        <v>0.1863903321741372</v>
       </c>
       <c r="H143" t="b">
         <v>0</v>
@@ -5141,16 +5141,16 @@
         <v>36</v>
       </c>
       <c r="D144">
-        <v>1.234567437739521</v>
+        <v>1.26686999538307</v>
       </c>
       <c r="E144">
-        <v>0.8142506270332842</v>
+        <v>0.7318465149313357</v>
       </c>
       <c r="F144">
-        <v>1.871852114968557</v>
+        <v>2.193027571296807</v>
       </c>
       <c r="G144">
-        <v>0.3210488890640329</v>
+        <v>0.3981636867987751</v>
       </c>
       <c r="H144" t="b">
         <v>0</v>
@@ -5167,19 +5167,19 @@
         <v>38</v>
       </c>
       <c r="D145">
-        <v>0.9957234354661352</v>
+        <v>0.9963031920893881</v>
       </c>
       <c r="E145">
-        <v>0.9916461979420106</v>
+        <v>0.9890251620048061</v>
       </c>
       <c r="F145">
-        <v>0.9998174368984587</v>
+        <v>1.003634779680844</v>
       </c>
       <c r="G145">
-        <v>0.0406406798344638</v>
+        <v>0.3221403255242635</v>
       </c>
       <c r="H145" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -5193,16 +5193,16 @@
         <v>36</v>
       </c>
       <c r="D146">
-        <v>1.156059428699619</v>
+        <v>1.03657656278044</v>
       </c>
       <c r="E146">
-        <v>0.8994926346453671</v>
+        <v>0.7805209914903903</v>
       </c>
       <c r="F146">
-        <v>1.485808055796039</v>
+        <v>1.376633021046609</v>
       </c>
       <c r="G146">
-        <v>0.2573621803012853</v>
+        <v>0.8040063913469427</v>
       </c>
       <c r="H146" t="b">
         <v>0</v>
@@ -5219,16 +5219,16 @@
         <v>38</v>
       </c>
       <c r="D147">
-        <v>1.002052594627793</v>
+        <v>1.000818303750079</v>
       </c>
       <c r="E147">
-        <v>0.9993436769003602</v>
+        <v>0.9978262409150433</v>
       </c>
       <c r="F147">
-        <v>1.004768855409896</v>
+        <v>1.003819338527965</v>
       </c>
       <c r="G147">
-        <v>0.1376466456627679</v>
+        <v>0.5923382031385989</v>
       </c>
       <c r="H147" t="b">
         <v>0</v>
@@ -5245,16 +5245,16 @@
         <v>36</v>
       </c>
       <c r="D148">
-        <v>0.9023857568191853</v>
+        <v>0.9431983440912166</v>
       </c>
       <c r="E148">
-        <v>0.8024363030130939</v>
+        <v>0.8063088234422057</v>
       </c>
       <c r="F148">
-        <v>1.014784663969579</v>
+        <v>1.103328018287746</v>
       </c>
       <c r="G148">
-        <v>0.08635937461803901</v>
+        <v>0.4648252104778178</v>
       </c>
       <c r="H148" t="b">
         <v>0</v>
@@ -5271,16 +5271,16 @@
         <v>38</v>
       </c>
       <c r="D149">
-        <v>1.001519624013953</v>
+        <v>1.002027106797722</v>
       </c>
       <c r="E149">
-        <v>0.9972413639245596</v>
+        <v>0.9982360149143585</v>
       </c>
       <c r="F149">
-        <v>1.005816238245135</v>
+        <v>1.005832596456214</v>
       </c>
       <c r="G149">
-        <v>0.4869222246605163</v>
+        <v>0.295065629906791</v>
       </c>
       <c r="H149" t="b">
         <v>0</v>
@@ -5297,16 +5297,16 @@
         <v>36</v>
       </c>
       <c r="D150">
-        <v>2.195115670934099</v>
+        <v>2.680478823410729</v>
       </c>
       <c r="E150">
-        <v>1.019796994739372</v>
+        <v>1.040254942659733</v>
       </c>
       <c r="F150">
-        <v>4.72499216377072</v>
+        <v>6.906928703825985</v>
       </c>
       <c r="G150">
-        <v>0.04442247164925284</v>
+        <v>0.04118276410044402</v>
       </c>
       <c r="H150" t="b">
         <v>1</v>
@@ -5323,16 +5323,16 @@
         <v>38</v>
       </c>
       <c r="D151">
-        <v>1.006793719955475</v>
+        <v>1.006269117747442</v>
       </c>
       <c r="E151">
-        <v>0.9971082282849576</v>
+        <v>0.9920209787062831</v>
       </c>
       <c r="F151">
-        <v>1.016573292435115</v>
+        <v>1.020721899100097</v>
       </c>
       <c r="G151">
-        <v>0.1698157095090134</v>
+        <v>0.3903769510481702</v>
       </c>
       <c r="H151" t="b">
         <v>0</v>
@@ -5349,19 +5349,19 @@
         <v>36</v>
       </c>
       <c r="D152">
-        <v>1.433857389476993</v>
+        <v>1.218117076085798</v>
       </c>
       <c r="E152">
-        <v>1.086212342539027</v>
+        <v>0.7694658626838642</v>
       </c>
       <c r="F152">
-        <v>1.892767125580613</v>
+        <v>1.928362625310435</v>
       </c>
       <c r="G152">
-        <v>0.01096900808579572</v>
+        <v>0.3998758081434338</v>
       </c>
       <c r="H152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -5375,16 +5375,16 @@
         <v>38</v>
       </c>
       <c r="D153">
-        <v>0.9986277362626339</v>
+        <v>1.004550495932971</v>
       </c>
       <c r="E153">
-        <v>0.9946265188929158</v>
+        <v>0.9982930495793043</v>
       </c>
       <c r="F153">
-        <v>1.002645049865597</v>
+        <v>1.010847164872516</v>
       </c>
       <c r="G153">
-        <v>0.5026128674126275</v>
+        <v>0.1544188956125638</v>
       </c>
       <c r="H153" t="b">
         <v>0</v>
@@ -5401,16 +5401,16 @@
         <v>36</v>
       </c>
       <c r="D154">
-        <v>0.7982520074549032</v>
+        <v>0.6597148798130701</v>
       </c>
       <c r="E154">
-        <v>0.6468162175245196</v>
+        <v>0.4915145878635352</v>
       </c>
       <c r="F154">
-        <v>0.9851426883581929</v>
+        <v>0.8854746804943452</v>
       </c>
       <c r="G154">
-        <v>0.0357790487776485</v>
+        <v>0.005606416676221418</v>
       </c>
       <c r="H154" t="b">
         <v>1</v>
@@ -5427,19 +5427,19 @@
         <v>38</v>
       </c>
       <c r="D155">
-        <v>0.9962831359944394</v>
+        <v>0.9955063749619395</v>
       </c>
       <c r="E155">
-        <v>0.9932225756336276</v>
+        <v>0.9909043270869855</v>
       </c>
       <c r="F155">
-        <v>0.9993531273025051</v>
+        <v>1.000129796085616</v>
       </c>
       <c r="G155">
-        <v>0.01768363439780558</v>
+        <v>0.05677169351712199</v>
       </c>
       <c r="H155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -5453,16 +5453,16 @@
         <v>36</v>
       </c>
       <c r="D156">
-        <v>0.9399682069738945</v>
+        <v>0.9475561323074998</v>
       </c>
       <c r="E156">
-        <v>0.8509994952713689</v>
+        <v>0.7672079218266923</v>
       </c>
       <c r="F156">
-        <v>1.038238253995642</v>
+        <v>1.170298948081469</v>
       </c>
       <c r="G156">
-        <v>0.222351498904361</v>
+        <v>0.6170172682551658</v>
       </c>
       <c r="H156" t="b">
         <v>0</v>
@@ -5479,16 +5479,16 @@
         <v>38</v>
       </c>
       <c r="D157">
-        <v>1.001025719071907</v>
+        <v>1.000490775182551</v>
       </c>
       <c r="E157">
-        <v>0.9992441068897225</v>
+        <v>0.9964919765632386</v>
       </c>
       <c r="F157">
-        <v>1.002810507797187</v>
+        <v>1.0045056204844</v>
       </c>
       <c r="G157">
-        <v>0.2593307953335477</v>
+        <v>0.810232941599675</v>
       </c>
       <c r="H157" t="b">
         <v>0</v>
@@ -5505,16 +5505,16 @@
         <v>36</v>
       </c>
       <c r="D158">
-        <v>1.129609763784263</v>
+        <v>0.9980911476081942</v>
       </c>
       <c r="E158">
-        <v>0.9321097322334401</v>
+        <v>0.6237686061147566</v>
       </c>
       <c r="F158">
-        <v>1.368957081243273</v>
+        <v>1.597044046731923</v>
       </c>
       <c r="G158">
-        <v>0.2138885092389752</v>
+        <v>0.9936435782563572</v>
       </c>
       <c r="H158" t="b">
         <v>0</v>
@@ -5531,16 +5531,16 @@
         <v>38</v>
       </c>
       <c r="D159">
-        <v>1.002818313869798</v>
+        <v>1.005823015162432</v>
       </c>
       <c r="E159">
-        <v>0.9980609921540684</v>
+        <v>0.9948452006777513</v>
       </c>
       <c r="F159">
-        <v>1.00759831166453</v>
+        <v>1.016921966494109</v>
       </c>
       <c r="G159">
-        <v>0.2460534334292394</v>
+        <v>0.2997573431493086</v>
       </c>
       <c r="H159" t="b">
         <v>0</v>
@@ -5557,16 +5557,16 @@
         <v>36</v>
       </c>
       <c r="D160">
-        <v>1.337192582520458</v>
+        <v>0.6194093518317761</v>
       </c>
       <c r="E160">
-        <v>0.8100560766800907</v>
+        <v>0.2962425273776819</v>
       </c>
       <c r="F160">
-        <v>2.207358298052599</v>
+        <v>1.295114339365326</v>
       </c>
       <c r="G160">
-        <v>0.255855807404642</v>
+        <v>0.2030894335255272</v>
       </c>
       <c r="H160" t="b">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>38</v>
       </c>
       <c r="D161">
-        <v>1.001783368664168</v>
+        <v>1.000110620967105</v>
       </c>
       <c r="E161">
-        <v>0.9979383035347731</v>
+        <v>0.9945679198412527</v>
       </c>
       <c r="F161">
-        <v>1.005643248863591</v>
+        <v>1.005684211422039</v>
       </c>
       <c r="G161">
-        <v>0.3638210796066412</v>
+        <v>0.9688819924051735</v>
       </c>
       <c r="H161" t="b">
         <v>0</v>
@@ -5609,16 +5609,16 @@
         <v>36</v>
       </c>
       <c r="D162">
-        <v>1.126869318574289</v>
+        <v>1.694258485187974</v>
       </c>
       <c r="E162">
-        <v>0.754711487438179</v>
+        <v>0.9456683700702055</v>
       </c>
       <c r="F162">
-        <v>1.68254290848872</v>
+        <v>3.035431770249802</v>
       </c>
       <c r="G162">
-        <v>0.5592194480468063</v>
+        <v>0.07636231459015001</v>
       </c>
       <c r="H162" t="b">
         <v>0</v>
@@ -5635,16 +5635,16 @@
         <v>38</v>
       </c>
       <c r="D163">
-        <v>0.9988363448156315</v>
+        <v>0.9997625739240313</v>
       </c>
       <c r="E163">
-        <v>0.9950463165111983</v>
+        <v>0.9952772815133745</v>
       </c>
       <c r="F163">
-        <v>1.002640808945122</v>
+        <v>1.004268079644469</v>
       </c>
       <c r="G163">
-        <v>0.5483215263506696</v>
+        <v>0.9175627819028841</v>
       </c>
       <c r="H163" t="b">
         <v>0</v>
@@ -5691,13 +5691,13 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>1.206119629834834</v>
+        <v>1.214137605873372</v>
       </c>
       <c r="E2">
-        <v>1.077599277223588</v>
+        <v>1.075199397872057</v>
       </c>
       <c r="F2">
-        <v>1.274728468598954</v>
+        <v>1.283811394553786</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -5711,13 +5711,13 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>1.079272403340275</v>
+        <v>1.039724569909015</v>
       </c>
       <c r="E3">
-        <v>0.9578656640321084</v>
+        <v>0.8758030140422388</v>
       </c>
       <c r="F3">
-        <v>1.210073565282102</v>
+        <v>1.202099347177008</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5731,13 +5731,13 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>1.035859625851937</v>
+        <v>0.9447802646365325</v>
       </c>
       <c r="E4">
-        <v>0.9076004516344001</v>
+        <v>0.8491001394663481</v>
       </c>
       <c r="F4">
-        <v>1.114019500531834</v>
+        <v>1.092387409912834</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5751,13 +5751,13 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>1.091759151660837</v>
+        <v>1.100311250702104</v>
       </c>
       <c r="E5">
-        <v>1.002250583178883</v>
+        <v>1.003405295320381</v>
       </c>
       <c r="F5">
-        <v>1.283547822990354</v>
+        <v>1.283918331914172</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5771,13 +5771,13 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>1.086924589495186</v>
+        <v>1.072765776636823</v>
       </c>
       <c r="E6">
-        <v>0.9803189142418653</v>
+        <v>0.9817766368998766</v>
       </c>
       <c r="F6">
-        <v>1.148801739930623</v>
+        <v>1.142688523901328</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5791,13 +5791,13 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>1.03886911033154</v>
+        <v>1.075122259794985</v>
       </c>
       <c r="E7">
-        <v>0.9692988475837958</v>
+        <v>0.9291362887894417</v>
       </c>
       <c r="F7">
-        <v>1.141128082925838</v>
+        <v>1.217609818427448</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5811,13 +5811,13 @@
         <v>27</v>
       </c>
       <c r="D8">
-        <v>1.15071427551223</v>
+        <v>1.159050467433507</v>
       </c>
       <c r="E8">
-        <v>0.9871122455506962</v>
+        <v>0.9915045957102796</v>
       </c>
       <c r="F8">
-        <v>1.371173548385181</v>
+        <v>1.371540123596686</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -5831,13 +5831,13 @@
         <v>27</v>
       </c>
       <c r="D9">
-        <v>1.121065122361285</v>
+        <v>1.068661252050839</v>
       </c>
       <c r="E9">
-        <v>0.8404517171928902</v>
+        <v>0.7110032265118305</v>
       </c>
       <c r="F9">
-        <v>1.286685752323092</v>
+        <v>1.381529298457857</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -5851,13 +5851,13 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>1.142569072053209</v>
+        <v>1.039573425939488</v>
       </c>
       <c r="E10">
-        <v>0.9062703422427538</v>
+        <v>0.849926363290493</v>
       </c>
       <c r="F10">
-        <v>1.302821495879335</v>
+        <v>1.411778374615322</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -5871,13 +5871,13 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>1.001418276192597</v>
+        <v>1.001414695650373</v>
       </c>
       <c r="E11">
-        <v>1.000581804581401</v>
+        <v>1.000601784129756</v>
       </c>
       <c r="F11">
-        <v>1.002929290623765</v>
+        <v>1.002959126462603</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -5891,13 +5891,13 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>1.000331682475684</v>
+        <v>0.9999818811305303</v>
       </c>
       <c r="E12">
-        <v>0.9989346681266309</v>
+        <v>0.9972856091063507</v>
       </c>
       <c r="F12">
-        <v>1.001987997280708</v>
+        <v>1.001517152653051</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -5911,13 +5911,13 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>0.9996769005189915</v>
+        <v>0.9988453263776078</v>
       </c>
       <c r="E13">
-        <v>0.9984172143836534</v>
+        <v>0.9951133766702143</v>
       </c>
       <c r="F13">
-        <v>1.001160806205631</v>
+        <v>1.00033864411195</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -5931,13 +5931,13 @@
         <v>27</v>
       </c>
       <c r="D14">
-        <v>1.00172439015888</v>
+        <v>1.001691899549071</v>
       </c>
       <c r="E14">
-        <v>1.000930306123325</v>
+        <v>1.000917332292813</v>
       </c>
       <c r="F14">
-        <v>1.003284054237898</v>
+        <v>1.003048732516969</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5951,13 +5951,13 @@
         <v>27</v>
       </c>
       <c r="D15">
-        <v>1.0005915721274</v>
+        <v>1.00033723853822</v>
       </c>
       <c r="E15">
-        <v>0.9992923283609938</v>
+        <v>0.9981119794289457</v>
       </c>
       <c r="F15">
-        <v>1.002697223127972</v>
+        <v>1.002580762086286</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -5971,13 +5971,13 @@
         <v>27</v>
       </c>
       <c r="D16">
-        <v>0.999904402684428</v>
+        <v>0.9981423827089951</v>
       </c>
       <c r="E16">
-        <v>0.9976113767522496</v>
+        <v>0.9944426530777867</v>
       </c>
       <c r="F16">
-        <v>1.001626906543196</v>
+        <v>1.000679743279464</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5991,13 +5991,13 @@
         <v>27</v>
       </c>
       <c r="D17">
-        <v>1.00263849031457</v>
+        <v>1.00269705244031</v>
       </c>
       <c r="E17">
-        <v>1.001879640237071</v>
+        <v>1.001880583801842</v>
       </c>
       <c r="F17">
-        <v>1.004062357418997</v>
+        <v>1.004124934570562</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -6011,13 +6011,13 @@
         <v>27</v>
       </c>
       <c r="D18">
-        <v>1.000822252648445</v>
+        <v>1.000876810830009</v>
       </c>
       <c r="E18">
-        <v>0.9985059036259272</v>
+        <v>0.9983575983820731</v>
       </c>
       <c r="F18">
-        <v>1.003909724598483</v>
+        <v>1.004215703519287</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -6031,13 +6031,13 @@
         <v>27</v>
       </c>
       <c r="D19">
-        <v>1.002340606644654</v>
+        <v>1.000517858106629</v>
       </c>
       <c r="E19">
-        <v>0.9987861501329112</v>
+        <v>0.9987395362828152</v>
       </c>
       <c r="F19">
-        <v>1.004148904715142</v>
+        <v>1.003266097674548</v>
       </c>
     </row>
   </sheetData>
@@ -6078,7 +6078,7 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>50631.92666211304</v>
+        <v>44137.15746542835</v>
       </c>
       <c r="E2">
         <v>27</v>
@@ -6095,7 +6095,7 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>154836.3006257973</v>
+        <v>154898.4274485812</v>
       </c>
       <c r="E3">
         <v>27</v>
@@ -6112,7 +6112,7 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>17208.59020390917</v>
+        <v>8326.650883030003</v>
       </c>
       <c r="E4">
         <v>27</v>
@@ -6129,7 +6129,7 @@
         <v>39</v>
       </c>
       <c r="D5">
-        <v>48113.11078742489</v>
+        <v>36658.59181863381</v>
       </c>
       <c r="E5">
         <v>27</v>
@@ -6146,7 +6146,7 @@
         <v>34</v>
       </c>
       <c r="D6">
-        <v>82352.43483693282</v>
+        <v>82497.74686356891</v>
       </c>
       <c r="E6">
         <v>27</v>
@@ -6163,7 +6163,7 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>10902.00944525989</v>
+        <v>4482.969909804469</v>
       </c>
       <c r="E7">
         <v>27</v>
@@ -6180,7 +6180,7 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>3809671.452987808</v>
+        <v>3182539.675828475</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -6197,7 +6197,7 @@
         <v>34</v>
       </c>
       <c r="D9">
-        <v>22299664.04366531</v>
+        <v>22341710.07139863</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -6214,7 +6214,7 @@
         <v>40</v>
       </c>
       <c r="D10">
-        <v>1196877.988762059</v>
+        <v>943011.5924637372</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -6231,7 +6231,7 @@
         <v>39</v>
       </c>
       <c r="D11">
-        <v>50631.92666211304</v>
+        <v>44137.15746542835</v>
       </c>
       <c r="E11">
         <v>27</v>
@@ -6248,7 +6248,7 @@
         <v>34</v>
       </c>
       <c r="D12">
-        <v>154836.3006257973</v>
+        <v>154898.4274485812</v>
       </c>
       <c r="E12">
         <v>27</v>
@@ -6265,7 +6265,7 @@
         <v>40</v>
       </c>
       <c r="D13">
-        <v>17208.59020390917</v>
+        <v>8326.650883030003</v>
       </c>
       <c r="E13">
         <v>27</v>
@@ -6282,7 +6282,7 @@
         <v>39</v>
       </c>
       <c r="D14">
-        <v>48113.11078742489</v>
+        <v>36658.59181863381</v>
       </c>
       <c r="E14">
         <v>27</v>
@@ -6299,7 +6299,7 @@
         <v>34</v>
       </c>
       <c r="D15">
-        <v>82352.43483693282</v>
+        <v>82497.74686356891</v>
       </c>
       <c r="E15">
         <v>27</v>
@@ -6316,7 +6316,7 @@
         <v>40</v>
       </c>
       <c r="D16">
-        <v>10902.00944525989</v>
+        <v>4482.969909804469</v>
       </c>
       <c r="E16">
         <v>27</v>
@@ -6333,7 +6333,7 @@
         <v>39</v>
       </c>
       <c r="D17">
-        <v>3809671.452987808</v>
+        <v>3182539.675828475</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -6350,7 +6350,7 @@
         <v>34</v>
       </c>
       <c r="D18">
-        <v>22299664.04366531</v>
+        <v>22341710.07139863</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6367,7 +6367,7 @@
         <v>40</v>
       </c>
       <c r="D19">
-        <v>1196877.988762059</v>
+        <v>943011.5924637372</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -6384,7 +6384,7 @@
         <v>39</v>
       </c>
       <c r="D20">
-        <v>1679.436130483995</v>
+        <v>1515.73782416799</v>
       </c>
       <c r="E20">
         <v>27</v>
@@ -6401,7 +6401,7 @@
         <v>34</v>
       </c>
       <c r="D21">
-        <v>2028.672693259805</v>
+        <v>2029.288746523246</v>
       </c>
       <c r="E21">
         <v>27</v>
@@ -6418,7 +6418,7 @@
         <v>40</v>
       </c>
       <c r="D22">
-        <v>1390.235023883946</v>
+        <v>1055.691127590658</v>
       </c>
       <c r="E22">
         <v>27</v>
@@ -6435,7 +6435,7 @@
         <v>39</v>
       </c>
       <c r="D23">
-        <v>1622.409282563199</v>
+        <v>1503.484948945781</v>
       </c>
       <c r="E23">
         <v>27</v>
@@ -6452,7 +6452,7 @@
         <v>34</v>
       </c>
       <c r="D24">
-        <v>1966.483871147273</v>
+        <v>1966.893493218124</v>
       </c>
       <c r="E24">
         <v>27</v>
@@ -6469,7 +6469,7 @@
         <v>40</v>
       </c>
       <c r="D25">
-        <v>1315.429368554363</v>
+        <v>1013.547477481431</v>
       </c>
       <c r="E25">
         <v>27</v>
@@ -6486,7 +6486,7 @@
         <v>39</v>
       </c>
       <c r="D26">
-        <v>45083.02696589466</v>
+        <v>39653.76368859795</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -6503,7 +6503,7 @@
         <v>34</v>
       </c>
       <c r="D27">
-        <v>55642.72002909351</v>
+        <v>55746.78999480681</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -6520,7 +6520,7 @@
         <v>40</v>
       </c>
       <c r="D28">
-        <v>36264.08925650062</v>
+        <v>27273.94343029732</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -6533,7 +6533,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1">
@@ -6582,28 +6582,28 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>1.003215201590385</v>
+        <v>1.003229356309664</v>
       </c>
       <c r="E2">
-        <v>1.001055086718301</v>
+        <v>1.001066121801487</v>
       </c>
       <c r="F2">
-        <v>1.005379977640782</v>
+        <v>1.005397265417686</v>
       </c>
       <c r="G2">
-        <v>0.003513512821085847</v>
+        <v>0.003417373666556776</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.004631114389851109</v>
+        <v>0.004651469742536139</v>
       </c>
       <c r="J2">
-        <v>0.001521365930766363</v>
+        <v>0.001537269323348692</v>
       </c>
       <c r="K2">
-        <v>0.007740862848935938</v>
+        <v>0.007765670161723882</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -6617,28 +6617,28 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>1.006357317876335</v>
+        <v>1.00637747622965</v>
       </c>
       <c r="E3">
-        <v>1.002213583174068</v>
+        <v>1.002236711144921</v>
       </c>
       <c r="F3">
-        <v>1.010518185191422</v>
+        <v>1.010535348984948</v>
       </c>
       <c r="G3">
-        <v>0.002609896420016327</v>
+        <v>0.002510723575060639</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.009142640332670824</v>
+        <v>0.009171538681768683</v>
       </c>
       <c r="J3">
-        <v>0.003189996108096567</v>
+        <v>0.003223288636179709</v>
       </c>
       <c r="K3">
-        <v>0.0150952845572451</v>
+        <v>0.01511978872735769</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -6652,28 +6652,28 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>3.862423238310198</v>
+        <v>3.860225971868828</v>
       </c>
       <c r="E4">
-        <v>1.894136206516865</v>
+        <v>1.892487413930742</v>
       </c>
       <c r="F4">
-        <v>7.876050951621889</v>
+        <v>7.873946449630639</v>
       </c>
       <c r="G4">
-        <v>0.0002015933206724933</v>
+        <v>0.0002041111880753546</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1.949506261221631</v>
+        <v>1.948685303180487</v>
       </c>
       <c r="J4">
-        <v>0.9215400781140981</v>
+        <v>0.9202837055372516</v>
       </c>
       <c r="K4">
-        <v>2.977472444329164</v>
+        <v>2.977086900823723</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -6687,28 +6687,28 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>1.004398142171862</v>
+        <v>1.004396335303877</v>
       </c>
       <c r="E5">
-        <v>1.001291958522772</v>
+        <v>1.00128872475704</v>
       </c>
       <c r="F5">
-        <v>1.007513961748594</v>
+        <v>1.007513590664514</v>
       </c>
       <c r="G5">
-        <v>0.005486907740558856</v>
+        <v>0.005527895555117682</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>0.006331265181706998</v>
+        <v>0.006328669834587017</v>
       </c>
       <c r="J5">
-        <v>0.00186269914774459</v>
+        <v>0.001858039822082714</v>
       </c>
       <c r="K5">
-        <v>0.01079983121566924</v>
+        <v>0.01079929984709134</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -6722,28 +6722,28 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>1.792531771444922</v>
+        <v>1.807151754191344</v>
       </c>
       <c r="E6">
-        <v>1.233824698489254</v>
+        <v>1.24926204359737</v>
       </c>
       <c r="F6">
-        <v>2.604235557590808</v>
+        <v>2.614181291598897</v>
       </c>
       <c r="G6">
-        <v>0.002194631295855725</v>
+        <v>0.001681252370134909</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.8419986899731037</v>
+        <v>0.8537176605060972</v>
       </c>
       <c r="J6">
-        <v>0.3031374312897469</v>
+        <v>0.3210761265424393</v>
       </c>
       <c r="K6">
-        <v>1.380859948656461</v>
+        <v>1.386359194469755</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -6757,28 +6757,28 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>1.006055032341569</v>
+        <v>1.00609742473109</v>
       </c>
       <c r="E7">
-        <v>1.002052018058762</v>
+        <v>1.002115289355005</v>
       </c>
       <c r="F7">
-        <v>1.01007403793327</v>
+        <v>1.010095384037137</v>
       </c>
       <c r="G7">
-        <v>0.003000224518672711</v>
+        <v>0.002662309569892121</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.008709224342978722</v>
+        <v>0.008770014259694125</v>
       </c>
       <c r="J7">
-        <v>0.002957402991701787</v>
+        <v>0.003048494374155718</v>
       </c>
       <c r="K7">
-        <v>0.01446104569425536</v>
+        <v>0.01449153414523244</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -6792,28 +6792,28 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>1.826955941952724</v>
+        <v>1.82603404300949</v>
       </c>
       <c r="E8">
-        <v>1.13974596034966</v>
+        <v>1.138415143377685</v>
       </c>
       <c r="F8">
-        <v>2.928519275306209</v>
+        <v>2.928984514679236</v>
       </c>
       <c r="G8">
-        <v>0.01230389404911613</v>
+        <v>0.01250029075135707</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.8694418430005791</v>
+        <v>0.8687136619394122</v>
       </c>
       <c r="J8">
-        <v>0.1887122958060201</v>
+        <v>0.1870267580615205</v>
       </c>
       <c r="K8">
-        <v>1.550171390195138</v>
+        <v>1.550400565817304</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -6827,28 +6827,28 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>1.00579085769352</v>
+        <v>1.0057884005098</v>
       </c>
       <c r="E9">
-        <v>1.001115724535675</v>
+        <v>1.00111148721907</v>
       </c>
       <c r="F9">
-        <v>1.01048782336234</v>
+        <v>1.010487163033315</v>
       </c>
       <c r="G9">
-        <v>0.01513786645159253</v>
+        <v>0.01521989864522346</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.008330344967826746</v>
+        <v>0.008326820406959123</v>
       </c>
       <c r="J9">
-        <v>0.001608752958836883</v>
+        <v>0.001602646603257411</v>
       </c>
       <c r="K9">
-        <v>0.0150519369768168</v>
+        <v>0.0150509942106607</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -6862,28 +6862,28 @@
         <v>36</v>
       </c>
       <c r="D10">
-        <v>1.743498731076022</v>
+        <v>1.62714357040853</v>
       </c>
       <c r="E10">
-        <v>1.265848566853216</v>
+        <v>1.151900877030109</v>
       </c>
       <c r="F10">
-        <v>2.401383471026345</v>
+        <v>2.298458358281652</v>
       </c>
       <c r="G10">
-        <v>0.0006660644161850444</v>
+        <v>0.005738122783153863</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10">
-        <v>0.8019853141169139</v>
+        <v>0.7023415522877555</v>
       </c>
       <c r="J10">
-        <v>0.3401048258426865</v>
+        <v>0.2040165758342204</v>
       </c>
       <c r="K10">
-        <v>1.263865802391141</v>
+        <v>1.200666528741291</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -6897,28 +6897,28 @@
         <v>36</v>
       </c>
       <c r="D11">
-        <v>1.782968501945143</v>
+        <v>1.825259116570878</v>
       </c>
       <c r="E11">
-        <v>1.185513538245327</v>
+        <v>1.211537909014057</v>
       </c>
       <c r="F11">
-        <v>2.681518663746089</v>
+        <v>2.749869251170454</v>
       </c>
       <c r="G11">
-        <v>0.005482036048487182</v>
+        <v>0.004006431250359586</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11">
-        <v>0.834281216429577</v>
+        <v>0.8681012857220216</v>
       </c>
       <c r="J11">
-        <v>0.2455121381028166</v>
+        <v>0.2768395474148755</v>
       </c>
       <c r="K11">
-        <v>1.423050294756337</v>
+        <v>1.459363024029168</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -6932,28 +6932,28 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>2.243053342052165</v>
+        <v>2.248698418309647</v>
       </c>
       <c r="E12">
-        <v>1.681798606253442</v>
+        <v>1.685081826032201</v>
       </c>
       <c r="F12">
-        <v>2.991611645165785</v>
+        <v>3.000830285147042</v>
       </c>
       <c r="G12">
-        <v>3.837358373874807E-08</v>
+        <v>3.701772088163586E-08</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1.165463929563317</v>
+        <v>1.169090188646355</v>
       </c>
       <c r="J12">
-        <v>0.7500049546089574</v>
+        <v>0.7528186490597307</v>
       </c>
       <c r="K12">
-        <v>1.580922904517676</v>
+        <v>1.585361728232979</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -6967,28 +6967,28 @@
         <v>36</v>
       </c>
       <c r="D13">
-        <v>2.41360458941741</v>
+        <v>2.438401392462969</v>
       </c>
       <c r="E13">
-        <v>1.803949445190723</v>
+        <v>1.823090377434055</v>
       </c>
       <c r="F13">
-        <v>3.229296214252214</v>
+        <v>3.261385954509772</v>
       </c>
       <c r="G13">
-        <v>2.998540997817902E-09</v>
+        <v>1.885620054667856E-09</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>1.271189344853568</v>
+        <v>1.285935631803308</v>
       </c>
       <c r="J13">
-        <v>0.8511589083302044</v>
+        <v>0.8663860829590426</v>
       </c>
       <c r="K13">
-        <v>1.691219781376933</v>
+        <v>1.705485180647573</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -7002,28 +7002,28 @@
         <v>38</v>
       </c>
       <c r="D14">
-        <v>1.005403301082382</v>
+        <v>1.005440098072981</v>
       </c>
       <c r="E14">
-        <v>1.002905530282115</v>
+        <v>1.002948753095876</v>
       </c>
       <c r="F14">
-        <v>1.007907292666942</v>
+        <v>1.007937631601371</v>
       </c>
       <c r="G14">
-        <v>2.175799710974723E-05</v>
+        <v>1.818565195596919E-05</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0.007774331014192191</v>
+        <v>0.007827131581242848</v>
       </c>
       <c r="J14">
-        <v>0.004185716206982537</v>
+        <v>0.004247891550019836</v>
       </c>
       <c r="K14">
-        <v>0.01136294582140177</v>
+        <v>0.01140637161246589</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -7037,28 +7037,28 @@
         <v>36</v>
       </c>
       <c r="D15">
-        <v>0.7327446472218286</v>
+        <v>0.7371477453341434</v>
       </c>
       <c r="E15">
-        <v>0.5493692643380499</v>
+        <v>0.5531413673353172</v>
       </c>
       <c r="F15">
-        <v>0.9773293718555321</v>
+        <v>0.9823651430535789</v>
       </c>
       <c r="G15">
-        <v>0.03434406087895316</v>
+        <v>0.0373977154245982</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>-0.4486175709759292</v>
+        <v>-0.4399742895444202</v>
       </c>
       <c r="J15">
-        <v>-0.8641518969371188</v>
+        <v>-0.8542798551336065</v>
       </c>
       <c r="K15">
-        <v>-0.03308324501473961</v>
+        <v>-0.02566872395523412</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -7072,28 +7072,28 @@
         <v>36</v>
       </c>
       <c r="D16">
-        <v>1.454299226713854</v>
+        <v>1.449855870333512</v>
       </c>
       <c r="E16">
-        <v>1.171539085897946</v>
+        <v>1.166411652898281</v>
       </c>
       <c r="F16">
-        <v>1.805305743768205</v>
+        <v>1.802178535783081</v>
       </c>
       <c r="G16">
-        <v>0.0006858789009637938</v>
+        <v>0.0008172306462736407</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0.540324138915029</v>
+        <v>0.5359094895573649</v>
       </c>
       <c r="J16">
-        <v>0.2284050874408904</v>
+        <v>0.222077037924422</v>
       </c>
       <c r="K16">
-        <v>0.8522431903891673</v>
+        <v>0.8497419411903081</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -7107,28 +7107,28 @@
         <v>36</v>
       </c>
       <c r="D17">
-        <v>1.423269373598292</v>
+        <v>1.440749042005726</v>
       </c>
       <c r="E17">
-        <v>1.044745300229343</v>
+        <v>1.051979139750009</v>
       </c>
       <c r="F17">
-        <v>1.938937374858919</v>
+        <v>1.973192930929883</v>
       </c>
       <c r="G17">
-        <v>0.02525701657132073</v>
+        <v>0.02285977471647863</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0.5092087378839514</v>
+        <v>0.5268190604366925</v>
       </c>
       <c r="J17">
-        <v>0.06315126873347758</v>
+        <v>0.07310609695189223</v>
       </c>
       <c r="K17">
-        <v>0.9552662070344249</v>
+        <v>0.9805320239214926</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -7142,28 +7142,28 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>1.006152038726437</v>
+        <v>1.006256325682083</v>
       </c>
       <c r="E18">
-        <v>1.001830832363143</v>
+        <v>1.001899164535377</v>
       </c>
       <c r="F18">
-        <v>1.010491883789829</v>
+        <v>1.010632435695034</v>
       </c>
       <c r="G18">
-        <v>0.005223408932323592</v>
+        <v>0.004848567306493616</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.008848325961796809</v>
+        <v>0.008997852545502677</v>
       </c>
       <c r="J18">
-        <v>0.002638917799402532</v>
+        <v>0.002737316771524387</v>
       </c>
       <c r="K18">
-        <v>0.01505773412419086</v>
+        <v>0.01525838831948133</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -7177,28 +7177,28 @@
         <v>36</v>
       </c>
       <c r="D19">
-        <v>0.694245868799462</v>
+        <v>0.6950284753158306</v>
       </c>
       <c r="E19">
-        <v>0.5293974419246372</v>
+        <v>0.5297457267230347</v>
       </c>
       <c r="F19">
-        <v>0.9104262472309643</v>
+        <v>0.9118800910165855</v>
       </c>
       <c r="G19">
-        <v>0.008328675238015211</v>
+        <v>0.008645606452922982</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>-0.5264814077625959</v>
+        <v>-0.5248560086262148</v>
       </c>
       <c r="J19">
-        <v>-0.9175768712130167</v>
+        <v>-0.9166280499687315</v>
       </c>
       <c r="K19">
-        <v>-0.1353859443121752</v>
+        <v>-0.1330839672836982</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -7212,28 +7212,28 @@
         <v>38</v>
       </c>
       <c r="D20">
-        <v>1.007157960665007</v>
+        <v>1.007181893853036</v>
       </c>
       <c r="E20">
-        <v>1.001965451637281</v>
+        <v>1.0019772401803</v>
       </c>
       <c r="F20">
-        <v>1.012377378953884</v>
+        <v>1.012413582491006</v>
       </c>
       <c r="G20">
-        <v>0.006840843792516123</v>
+        <v>0.006784905578406887</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.01028997053068615</v>
+        <v>0.01032425301942029</v>
       </c>
       <c r="J20">
-        <v>0.002832764410506981</v>
+        <v>0.002849738221806977</v>
       </c>
       <c r="K20">
-        <v>0.01774717665086555</v>
+        <v>0.01779876781703362</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -7247,28 +7247,28 @@
         <v>36</v>
       </c>
       <c r="D21">
-        <v>2.457233350711959</v>
+        <v>2.45765070384205</v>
       </c>
       <c r="E21">
-        <v>1.817464859614444</v>
+        <v>1.817558536324501</v>
       </c>
       <c r="F21">
-        <v>3.322207693815892</v>
+        <v>3.323165037814745</v>
       </c>
       <c r="G21">
-        <v>5.140427668395842E-09</v>
+        <v>5.177208081313466E-09</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1.297034869474309</v>
+        <v>1.297279885749707</v>
       </c>
       <c r="J21">
-        <v>0.8619274701420736</v>
+        <v>0.8620018283567839</v>
       </c>
       <c r="K21">
-        <v>1.732142268806545</v>
+        <v>1.732557943142629</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -7282,28 +7282,28 @@
         <v>36</v>
       </c>
       <c r="D22">
-        <v>1.397460889535761</v>
+        <v>1.395488902305418</v>
       </c>
       <c r="E22">
-        <v>1.112821670582818</v>
+        <v>1.112143261816228</v>
       </c>
       <c r="F22">
-        <v>1.754905560707935</v>
+        <v>1.751023760443706</v>
       </c>
       <c r="G22">
-        <v>0.003978291096027964</v>
+        <v>0.004003781664126778</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>0.4828079072098845</v>
+        <v>0.4807706513458641</v>
       </c>
       <c r="J22">
-        <v>0.1542224196530634</v>
+        <v>0.153342642197397</v>
       </c>
       <c r="K22">
-        <v>0.8113933947667058</v>
+        <v>0.8081986604943314</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -7317,28 +7317,28 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>1.008014044221147</v>
+        <v>1.008142745354075</v>
       </c>
       <c r="E23">
-        <v>1.004482700047146</v>
+        <v>1.004635235270167</v>
       </c>
       <c r="F23">
-        <v>1.011557803135267</v>
+        <v>1.011662501302508</v>
       </c>
       <c r="G23">
-        <v>8.276745773741619E-06</v>
+        <v>5.100443461499252E-06</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>0.0115157394202236</v>
+        <v>0.01169992795897683</v>
       </c>
       <c r="J23">
-        <v>0.006452717111407184</v>
+        <v>0.006671780220016495</v>
       </c>
       <c r="K23">
-        <v>0.01657876172903987</v>
+        <v>0.01672807569793713</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -7352,28 +7352,28 @@
         <v>36</v>
       </c>
       <c r="D24">
-        <v>1.60152490241863</v>
+        <v>1.600990128837742</v>
       </c>
       <c r="E24">
-        <v>1.241261145149817</v>
+        <v>1.240402132041116</v>
       </c>
       <c r="F24">
-        <v>2.066351648151709</v>
+        <v>2.066401956612348</v>
       </c>
       <c r="G24">
-        <v>0.0002920278634266462</v>
+        <v>0.0003007886604986013</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0.6794462310295786</v>
+        <v>0.6789644127131703</v>
       </c>
       <c r="J24">
-        <v>0.3118066716148247</v>
+        <v>0.3108079108136576</v>
       </c>
       <c r="K24">
-        <v>1.047085790444332</v>
+        <v>1.047120914612683</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -7387,28 +7387,28 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>1.006683554039266</v>
+        <v>1.006684970589946</v>
       </c>
       <c r="E25">
-        <v>1.000714752482246</v>
+        <v>1.000715122516197</v>
       </c>
       <c r="F25">
-        <v>1.012687956742306</v>
+        <v>1.012690432281619</v>
       </c>
       <c r="G25">
-        <v>0.02813138746196116</v>
+        <v>0.02812559932757937</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>0.009610250608355034</v>
+        <v>0.009612280689402128</v>
       </c>
       <c r="J25">
-        <v>0.001030801521494751</v>
+        <v>0.001031334986247236</v>
       </c>
       <c r="K25">
-        <v>0.01818969969521537</v>
+        <v>0.01819322639255703</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -7416,34 +7416,34 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D26">
-        <v>1.00224695274611</v>
+        <v>1.404031362708315</v>
       </c>
       <c r="E26">
-        <v>1.000064873404088</v>
+        <v>1.016899383881381</v>
       </c>
       <c r="F26">
-        <v>1.004433793249514</v>
+        <v>1.938543870431254</v>
       </c>
       <c r="G26">
-        <v>0.04356009751976932</v>
+        <v>0.03922849375124827</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0.003238031093314464</v>
+        <v>0.4895751623649799</v>
       </c>
       <c r="J26">
-        <v>9.358950266136198E-05</v>
+        <v>0.02417694020189705</v>
       </c>
       <c r="K26">
-        <v>0.00638247268396775</v>
+        <v>0.9549733845280627</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -7457,28 +7457,28 @@
         <v>38</v>
       </c>
       <c r="D27">
-        <v>1.003258716520302</v>
+        <v>1.007150426020809</v>
       </c>
       <c r="E27">
-        <v>1.000026153075944</v>
+        <v>1.002526542951415</v>
       </c>
       <c r="F27">
-        <v>1.006501729157804</v>
+        <v>1.011795635502746</v>
       </c>
       <c r="G27">
-        <v>0.0481721187468114</v>
+        <v>0.002407482511004559</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0.004693690606804959</v>
+        <v>0.01027917755192438</v>
       </c>
       <c r="J27">
-        <v>3.773041958793102E-05</v>
+        <v>0.003640434064178518</v>
       </c>
       <c r="K27">
-        <v>0.009349650794021893</v>
+        <v>0.01691792103967058</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -7492,28 +7492,28 @@
         <v>36</v>
       </c>
       <c r="D28">
-        <v>1.731259606347015</v>
+        <v>1.913335281357969</v>
       </c>
       <c r="E28">
-        <v>1.227707656550429</v>
+        <v>1.315304003106505</v>
       </c>
       <c r="F28">
-        <v>2.44134652787816</v>
+        <v>2.783274353490086</v>
       </c>
       <c r="G28">
-        <v>0.001749064576476962</v>
+        <v>0.0006907129534753885</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28">
-        <v>0.7918220763550389</v>
+        <v>0.9360897050320982</v>
       </c>
       <c r="J28">
-        <v>0.2959670650596589</v>
+        <v>0.395396284753964</v>
       </c>
       <c r="K28">
-        <v>1.287677087650419</v>
+        <v>1.476783125310233</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -7527,28 +7527,28 @@
         <v>38</v>
       </c>
       <c r="D29">
-        <v>1.004491723350981</v>
+        <v>1.005132792492014</v>
       </c>
       <c r="E29">
-        <v>1.000565688923459</v>
+        <v>1.000599735869544</v>
       </c>
       <c r="F29">
-        <v>1.008433162810373</v>
+        <v>1.009686385400479</v>
       </c>
       <c r="G29">
-        <v>0.02489667103307695</v>
+        <v>0.02642301258550935</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29">
-        <v>0.006465676834083584</v>
+        <v>0.007386114751431238</v>
       </c>
       <c r="J29">
-        <v>0.0008158858575151257</v>
+        <v>0.0008649766120030719</v>
       </c>
       <c r="K29">
-        <v>0.01211546781065197</v>
+        <v>0.01390725289085958</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -7556,34 +7556,34 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
       </c>
       <c r="D30">
-        <v>2.411347833256714</v>
+        <v>1.6468267254479</v>
       </c>
       <c r="E30">
-        <v>1.321057614189294</v>
+        <v>1.046497819915044</v>
       </c>
       <c r="F30">
-        <v>4.40147220719071</v>
+        <v>2.591537423240519</v>
       </c>
       <c r="G30">
-        <v>0.004145873720786432</v>
+        <v>0.03104995700538832</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1.269839772516376</v>
+        <v>0.7196887666685234</v>
       </c>
       <c r="J30">
-        <v>0.4016933870182285</v>
+        <v>0.06556930614590942</v>
       </c>
       <c r="K30">
-        <v>2.137986158014523</v>
+        <v>1.373808227191138</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -7594,31 +7594,31 @@
         <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D31">
-        <v>1.01817126839501</v>
+        <v>2.442123694777389</v>
       </c>
       <c r="E31">
-        <v>1.008313153679677</v>
+        <v>1.286947545799433</v>
       </c>
       <c r="F31">
-        <v>1.028125764304405</v>
+        <v>4.634196754995511</v>
       </c>
       <c r="G31">
-        <v>0.0002859418729091099</v>
+        <v>0.006298574022959879</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0.02598026011833853</v>
+        <v>1.288136275395938</v>
       </c>
       <c r="J31">
-        <v>0.01194376889492286</v>
+        <v>0.3639532525040506</v>
       </c>
       <c r="K31">
-        <v>0.04001675134175426</v>
+        <v>2.212319298287826</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -7626,34 +7626,34 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D32">
-        <v>1.682585525333173</v>
+        <v>1.021281816430741</v>
       </c>
       <c r="E32">
-        <v>1.161346666102117</v>
+        <v>1.010250087021869</v>
       </c>
       <c r="F32">
-        <v>2.437768267388106</v>
+        <v>1.032434010123967</v>
       </c>
       <c r="G32">
-        <v>0.00594654094248549</v>
+        <v>0.0001445013238341735</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32">
-        <v>0.7506798384689501</v>
+        <v>0.03038102396885228</v>
       </c>
       <c r="J32">
-        <v>0.2157986860821461</v>
+        <v>0.0147124757935953</v>
       </c>
       <c r="K32">
-        <v>1.285560990855754</v>
+        <v>0.04604957214410946</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -7661,34 +7661,34 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
         <v>36</v>
       </c>
       <c r="D33">
-        <v>0.5968248106130553</v>
+        <v>1.762916087335205</v>
       </c>
       <c r="E33">
-        <v>0.4088521520594369</v>
+        <v>1.200400603992228</v>
       </c>
       <c r="F33">
-        <v>0.8712192237929732</v>
+        <v>2.589029962705176</v>
       </c>
       <c r="G33">
-        <v>0.007489017734945024</v>
+        <v>0.003834216225811201</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>-0.7446205837506352</v>
+        <v>0.8179638057604854</v>
       </c>
       <c r="J33">
-        <v>-1.290348860650369</v>
+        <v>0.2635159499538481</v>
       </c>
       <c r="K33">
-        <v>-0.1988923068509014</v>
+        <v>1.372411661567123</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -7696,34 +7696,34 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C34" t="s">
         <v>36</v>
       </c>
       <c r="D34">
-        <v>1.326280136915186</v>
+        <v>0.2176025726242568</v>
       </c>
       <c r="E34">
-        <v>1.047470624868235</v>
+        <v>0.118161058651417</v>
       </c>
       <c r="F34">
-        <v>1.679301509574111</v>
+        <v>0.4007316805816985</v>
       </c>
       <c r="G34">
-        <v>0.01902028417780025</v>
+        <v>9.820905816488161E-07</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34">
-        <v>0.4073855337105252</v>
+        <v>-2.200232481817872</v>
       </c>
       <c r="J34">
-        <v>0.06690978573736438</v>
+        <v>-3.081173437941594</v>
       </c>
       <c r="K34">
-        <v>0.7478612816836859</v>
+        <v>-1.319291525694149</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -7731,34 +7731,34 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D35">
-        <v>0.9948010784514612</v>
+        <v>0.3773424672244965</v>
       </c>
       <c r="E35">
-        <v>0.990384145072446</v>
+        <v>0.211677667091154</v>
       </c>
       <c r="F35">
-        <v>0.9992377105509896</v>
+        <v>0.6726611244716454</v>
       </c>
       <c r="G35">
-        <v>0.02168485174147801</v>
+        <v>0.0009520965417053778</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>-0.007520023323966729</v>
+        <v>-1.406053620484227</v>
       </c>
       <c r="J35">
-        <v>-0.01393987606261493</v>
+        <v>-2.240059028075791</v>
       </c>
       <c r="K35">
-        <v>-0.00110017058531859</v>
+        <v>-0.5720482128926618</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -7766,34 +7766,34 @@
         <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
         <v>36</v>
       </c>
       <c r="D36">
-        <v>0.549679815399025</v>
+        <v>1.584940539601711</v>
       </c>
       <c r="E36">
-        <v>0.4230501008552867</v>
+        <v>1.205600459963974</v>
       </c>
       <c r="F36">
-        <v>0.7142130420161803</v>
+        <v>2.083639312934593</v>
       </c>
       <c r="G36">
-        <v>7.489292794447667E-06</v>
+        <v>0.0009683964907444767</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>-0.8633365912409571</v>
+        <v>0.6644287174430195</v>
       </c>
       <c r="J36">
-        <v>-1.241099566352291</v>
+        <v>0.2697518724694239</v>
       </c>
       <c r="K36">
-        <v>-0.4855736161296227</v>
+        <v>1.059105562416615</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -7801,34 +7801,34 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s">
         <v>38</v>
       </c>
       <c r="D37">
-        <v>0.9947496826679273</v>
+        <v>0.9936440387742143</v>
       </c>
       <c r="E37">
-        <v>0.9916585778718816</v>
+        <v>0.9884864023902943</v>
       </c>
       <c r="F37">
-        <v>0.9978504227649458</v>
+        <v>0.9988285862142745</v>
       </c>
       <c r="G37">
-        <v>0.0009160023471972462</v>
+        <v>0.01633266811212109</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>-0.007594561198036025</v>
+        <v>-0.009198978984760138</v>
       </c>
       <c r="J37">
-        <v>-0.01208460007709616</v>
+        <v>-0.01670697449587032</v>
       </c>
       <c r="K37">
-        <v>-0.003104522318975916</v>
+        <v>-0.001690983473650117</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -7836,34 +7836,34 @@
         <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
         <v>36</v>
       </c>
       <c r="D38">
-        <v>1.10234236464664</v>
+        <v>0.2986877813344146</v>
       </c>
       <c r="E38">
-        <v>1.001260648791173</v>
+        <v>0.210669765425111</v>
       </c>
       <c r="F38">
-        <v>1.213628729304215</v>
+        <v>0.4234798028015514</v>
       </c>
       <c r="G38">
-        <v>0.04707352470716907</v>
+        <v>1.169090253718542E-11</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>0.1405723646242117</v>
+        <v>-1.743289873538622</v>
       </c>
       <c r="J38">
-        <v>0.001817586330885987</v>
+        <v>-2.246944816333222</v>
       </c>
       <c r="K38">
-        <v>0.2793271429175376</v>
+        <v>-1.239634930744022</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -7871,34 +7871,34 @@
         <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D39">
-        <v>1.40935950687995</v>
+        <v>0.9915282368920476</v>
       </c>
       <c r="E39">
-        <v>1.120391408328518</v>
+        <v>0.9870020009511259</v>
       </c>
       <c r="F39">
-        <v>1.77285741828045</v>
+        <v>0.9960752294391091</v>
       </c>
       <c r="G39">
-        <v>0.003379025709224402</v>
+        <v>0.0002678698631123622</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>0.4950396688768815</v>
+        <v>-0.012274236559249</v>
       </c>
       <c r="J39">
-        <v>0.164002825324981</v>
+        <v>-0.01887508542418967</v>
       </c>
       <c r="K39">
-        <v>0.826076512428782</v>
+        <v>-0.005673387694308323</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -7906,69 +7906,69 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
         <v>36</v>
       </c>
       <c r="D40">
-        <v>0.5952608127988548</v>
+        <v>1.384440813380027</v>
       </c>
       <c r="E40">
-        <v>0.392028550127741</v>
+        <v>1.041562633138535</v>
       </c>
       <c r="F40">
-        <v>0.9038510974226096</v>
+        <v>1.840193095231192</v>
       </c>
       <c r="G40">
-        <v>0.01491860108808649</v>
+        <v>0.02506290822823781</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>-0.7484061728741496</v>
+        <v>0.469303377960297</v>
       </c>
       <c r="J40">
-        <v>-1.350969370067697</v>
+        <v>0.05874959674912451</v>
       </c>
       <c r="K40">
-        <v>-0.1458429756806016</v>
+        <v>0.8798571591714696</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C41" t="s">
         <v>36</v>
       </c>
       <c r="D41">
-        <v>1.36064236700618</v>
+        <v>0.372338864408494</v>
       </c>
       <c r="E41">
-        <v>1.061163241212558</v>
+        <v>0.2141347559578605</v>
       </c>
       <c r="F41">
-        <v>1.744639824478563</v>
+        <v>0.6474251661243121</v>
       </c>
       <c r="G41">
-        <v>0.01518150123499625</v>
+        <v>0.0004647780613327123</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>0.4442879168434603</v>
+        <v>-1.425311883578256</v>
       </c>
       <c r="J41">
-        <v>0.08564660646246063</v>
+        <v>-2.223409118040343</v>
       </c>
       <c r="K41">
-        <v>0.8029292272244599</v>
+        <v>-0.627214649116169</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -7976,34 +7976,34 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D42">
-        <v>1.780577372630619</v>
+        <v>0.9913174362662867</v>
       </c>
       <c r="E42">
-        <v>1.122195202160349</v>
+        <v>0.9846298320986244</v>
       </c>
       <c r="F42">
-        <v>2.825226639554939</v>
+        <v>0.9980504626302357</v>
       </c>
       <c r="G42">
-        <v>0.01430864052065379</v>
+        <v>0.01156981426021445</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>0.832345127464637</v>
+        <v>-0.01258098864052718</v>
       </c>
       <c r="J42">
-        <v>0.1663236498273605</v>
+        <v>-0.02234664419458165</v>
       </c>
       <c r="K42">
-        <v>1.498366605101913</v>
+        <v>-0.002815333086472605</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -8017,28 +8017,28 @@
         <v>38</v>
       </c>
       <c r="D43">
-        <v>0.9920002770713133</v>
+        <v>0.9843444139317051</v>
       </c>
       <c r="E43">
-        <v>0.9854654275591588</v>
+        <v>0.9765532951679755</v>
       </c>
       <c r="F43">
-        <v>0.9985784606842412</v>
+        <v>0.9921976916496781</v>
       </c>
       <c r="G43">
-        <v>0.01722761667305362</v>
+        <v>9.946027333434123E-05</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>-0.01158757132223412</v>
+        <v>-0.02276490398412273</v>
       </c>
       <c r="J43">
-        <v>-0.02112283585995341</v>
+        <v>-0.03422931388188756</v>
       </c>
       <c r="K43">
-        <v>-0.002052306784514942</v>
+        <v>-0.01130049408635794</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -8046,34 +8046,34 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
       </c>
       <c r="D44">
-        <v>1.513699453304582</v>
+        <v>2.501912402849681</v>
       </c>
       <c r="E44">
-        <v>1.008526248772859</v>
+        <v>1.410088951257375</v>
       </c>
       <c r="F44">
-        <v>2.271915121418554</v>
+        <v>4.439128230847718</v>
       </c>
       <c r="G44">
-        <v>0.04539850766809601</v>
+        <v>0.001720806826475694</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44">
-        <v>0.5980787850661869</v>
+        <v>1.323031278637754</v>
       </c>
       <c r="J44">
-        <v>0.01224863326334203</v>
+        <v>0.4957861736100034</v>
       </c>
       <c r="K44">
-        <v>1.183908936869032</v>
+        <v>2.150276383665505</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -8081,34 +8081,34 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D45">
-        <v>0.5471947100177307</v>
+        <v>0.9936352859188957</v>
       </c>
       <c r="E45">
-        <v>0.3195606975898098</v>
+        <v>0.9884920094194855</v>
       </c>
       <c r="F45">
-        <v>0.9369802135546983</v>
+        <v>0.9988053236798006</v>
       </c>
       <c r="G45">
-        <v>0.02800868796189254</v>
+        <v>0.01589039477756067</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45">
-        <v>-0.8698738117908842</v>
+        <v>-0.009211687516273399</v>
       </c>
       <c r="J45">
-        <v>-1.645838111148862</v>
+        <v>-0.01669879106487288</v>
       </c>
       <c r="K45">
-        <v>-0.09390951243290654</v>
+        <v>-0.001724583967673918</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -8116,34 +8116,34 @@
         <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
         <v>38</v>
       </c>
       <c r="D46">
-        <v>0.9957234354661352</v>
+        <v>1.01022866016689</v>
       </c>
       <c r="E46">
-        <v>0.9916461979420106</v>
+        <v>1.003663029800558</v>
       </c>
       <c r="F46">
-        <v>0.9998174368984587</v>
+        <v>1.016837240707561</v>
       </c>
       <c r="G46">
-        <v>0.0406406798344638</v>
+        <v>0.002220573418480827</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>-0.006183008906978155</v>
+        <v>0.0146818766918093</v>
       </c>
       <c r="J46">
-        <v>-0.01210261088778901</v>
+        <v>0.005274979611570817</v>
       </c>
       <c r="K46">
-        <v>-0.0002634069261673097</v>
+        <v>0.0240887737720476</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -8151,34 +8151,34 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
         <v>36</v>
       </c>
       <c r="D47">
-        <v>2.195115670934099</v>
+        <v>1.845503316472165</v>
       </c>
       <c r="E47">
-        <v>1.019796994739372</v>
+        <v>1.006398147763925</v>
       </c>
       <c r="F47">
-        <v>4.72499216377072</v>
+        <v>3.384229689489346</v>
       </c>
       <c r="G47">
-        <v>0.04442247164925284</v>
+        <v>0.04763854704919675</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>1.134296964127893</v>
+        <v>0.8840143301891279</v>
       </c>
       <c r="J47">
-        <v>0.02828199157784156</v>
+        <v>0.009201172108994203</v>
       </c>
       <c r="K47">
-        <v>2.240311936677944</v>
+        <v>1.758827488269262</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -8186,34 +8186,34 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
         <v>36</v>
       </c>
       <c r="D48">
-        <v>1.433857389476993</v>
+        <v>0.3889996507540542</v>
       </c>
       <c r="E48">
-        <v>1.086212342539027</v>
+        <v>0.2059968617684318</v>
       </c>
       <c r="F48">
-        <v>1.892767125580613</v>
+        <v>0.7345778328258276</v>
       </c>
       <c r="G48">
-        <v>0.01096900808579572</v>
+        <v>0.003603122672916738</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>0.5199015416649656</v>
+        <v>-1.362159234934559</v>
       </c>
       <c r="J48">
-        <v>0.1193061616896832</v>
+        <v>-2.279305735855603</v>
       </c>
       <c r="K48">
-        <v>0.9204969216402478</v>
+        <v>-0.4450127340135142</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -8221,34 +8221,34 @@
         <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D49">
-        <v>0.7982520074549032</v>
+        <v>0.9889617119166448</v>
       </c>
       <c r="E49">
-        <v>0.6468162175245196</v>
+        <v>0.9825888722848624</v>
       </c>
       <c r="F49">
-        <v>0.9851426883581929</v>
+        <v>0.9953758842829188</v>
       </c>
       <c r="G49">
-        <v>0.0357790487776485</v>
+        <v>0.0007650883444557331</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>-0.3250838189785051</v>
+        <v>-0.01601342738856773</v>
       </c>
       <c r="J49">
-        <v>-0.6285722431492519</v>
+        <v>-0.02534019407478931</v>
       </c>
       <c r="K49">
-        <v>-0.02159539480775848</v>
+        <v>-0.006686660702346137</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -8256,34 +8256,104 @@
         <v>40</v>
       </c>
       <c r="B50" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50">
+        <v>1.007995284023513</v>
+      </c>
+      <c r="E50">
+        <v>1.000781586801849</v>
+      </c>
+      <c r="F50">
+        <v>1.015260978032779</v>
+      </c>
+      <c r="G50">
+        <v>0.02976759435018484</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>0.0114888891038939</v>
+      </c>
+      <c r="J50">
+        <v>0.001127150977245003</v>
+      </c>
+      <c r="K50">
+        <v>0.02185062723054251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51">
+        <v>2.680478823410729</v>
+      </c>
+      <c r="E51">
+        <v>1.040254942659733</v>
+      </c>
+      <c r="F51">
+        <v>6.906928703825985</v>
+      </c>
+      <c r="G51">
+        <v>0.04118276410044402</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1.422490737420647</v>
+      </c>
+      <c r="J51">
+        <v>0.05693714320963204</v>
+      </c>
+      <c r="K51">
+        <v>2.788044331631661</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" t="s">
         <v>66</v>
       </c>
-      <c r="C50" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50">
-        <v>0.9962831359944394</v>
-      </c>
-      <c r="E50">
-        <v>0.9932225756336276</v>
-      </c>
-      <c r="F50">
-        <v>0.9993531273025051</v>
-      </c>
-      <c r="G50">
-        <v>0.01768363439780558</v>
-      </c>
-      <c r="H50" t="b">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>-0.005372291503345888</v>
-      </c>
-      <c r="J50">
-        <v>-0.00981104099994789</v>
-      </c>
-      <c r="K50">
-        <v>-0.0009335420067438414</v>
+      <c r="C52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52">
+        <v>0.6597148798130701</v>
+      </c>
+      <c r="E52">
+        <v>0.4915145878635352</v>
+      </c>
+      <c r="F52">
+        <v>0.8854746804943452</v>
+      </c>
+      <c r="G52">
+        <v>0.005606416676221418</v>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>-0.6000854497422653</v>
+      </c>
+      <c r="J52">
+        <v>-1.024693859346812</v>
+      </c>
+      <c r="K52">
+        <v>-0.1754770401377182</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/GLM_Figures.xlsx
+++ b/source_data/GLM_Figures.xlsx
@@ -48,7 +48,7 @@
     <t>Pooled state+month FE IRRs for temperature and rainfall, by model family (* = Significant)</t>
   </si>
   <si>
-    <t>outputs/glm_*_pooled_fe.csv; plot_glm_results.R</t>
+    <t>outputs/regression/glm_*_pooled_fe.csv; plot_glm_results.R</t>
   </si>
   <si>
     <t>glm_fig2_state_heatmap</t>
@@ -57,7 +57,7 @@
     <t>Per-state NegBin IRRs (heatmap colour = log2 IRR)</t>
   </si>
   <si>
-    <t>outputs/glm_negbin_per_state.csv; plot_glm_results.R</t>
+    <t>outputs/regression/glm_negbin_per_state.csv; plot_glm_results.R</t>
   </si>
   <si>
     <t>glm_fig3_lag_profile</t>
@@ -66,7 +66,7 @@
     <t>Median and IQR of per-state NegBin IRRs by lag</t>
   </si>
   <si>
-    <t>outputs/glm_negbin_lagged.csv; plot_glm_results.R</t>
+    <t>outputs/regression/glm_negbin_lagged.csv; plot_glm_results.R</t>
   </si>
   <si>
     <t>glm_fig4_aic</t>
@@ -75,7 +75,7 @@
     <t>Median AIC across states per family × specification × virus</t>
   </si>
   <si>
-    <t>outputs/glm_*_*.csv; plot_glm_results.R</t>
+    <t>outputs/regression/glm_*_*.csv; plot_glm_results.R</t>
   </si>
   <si>
     <t>glm_fig5_forest</t>
